--- a/documents/SIZ_2026/Normy_SIZ_AI_specnaznacheniya_2026.xlsx
+++ b/documents/SIZ_2026/Normy_SIZ_AI_specnaznacheniya_2026.xlsx
@@ -11,7 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сборочный участок" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Швейный участок" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Смывающие средства" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Обоснование" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Подбор по прайсу" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Обоснование" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Механический участок'!$11:$12</definedName>
@@ -24,8 +25,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="7">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="# ##0.00"/>
+  </numFmts>
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -60,6 +63,16 @@
     <font>
       <name val="Times New Roman"/>
       <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <i val="1"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -138,7 +151,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -180,6 +193,21 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -804,9 +832,9 @@
           <t>При допуске к управлению подъёмными сооружениями (кран-балка, таль) с пола:</t>
         </is>
       </c>
-      <c r="D18" s="17" t="n"/>
-      <c r="E18" s="17" t="n"/>
-      <c r="F18" s="18" t="n"/>
+      <c r="D18" s="22" t="n"/>
+      <c r="E18" s="22" t="n"/>
+      <c r="F18" s="23" t="n"/>
     </row>
     <row r="19" ht="27" customHeight="1">
       <c r="A19" s="13" t="n"/>
@@ -978,9 +1006,9 @@
           <t>При допуске к управлению подъёмными сооружениями (кран-балка, таль) с пола:</t>
         </is>
       </c>
-      <c r="D26" s="17" t="n"/>
-      <c r="E26" s="17" t="n"/>
-      <c r="F26" s="18" t="n"/>
+      <c r="D26" s="22" t="n"/>
+      <c r="E26" s="22" t="n"/>
+      <c r="F26" s="23" t="n"/>
     </row>
     <row r="27" ht="27" customHeight="1">
       <c r="A27" s="12" t="n"/>
@@ -1014,9 +1042,9 @@
           <t>При выполнении работ в неотапливаемых помещениях, на открытом воздухе в холодный период года:</t>
         </is>
       </c>
-      <c r="D28" s="17" t="n"/>
-      <c r="E28" s="17" t="n"/>
-      <c r="F28" s="18" t="n"/>
+      <c r="D28" s="22" t="n"/>
+      <c r="E28" s="22" t="n"/>
+      <c r="F28" s="23" t="n"/>
     </row>
     <row r="29" ht="27" customHeight="1">
       <c r="A29" s="13" t="n"/>
@@ -1204,9 +1232,9 @@
           <t>При обработке деталей с образованием сливной стружки, при работе на станке без защитного экрана:</t>
         </is>
       </c>
-      <c r="D37" s="17" t="n"/>
-      <c r="E37" s="17" t="n"/>
-      <c r="F37" s="18" t="n"/>
+      <c r="D37" s="22" t="n"/>
+      <c r="E37" s="22" t="n"/>
+      <c r="F37" s="23" t="n"/>
     </row>
     <row r="38" ht="40.5" customHeight="1">
       <c r="A38" s="12" t="n"/>
@@ -1240,9 +1268,9 @@
           <t>При допуске к управлению подъёмными сооружениями (кран-балка, таль) с пола:</t>
         </is>
       </c>
-      <c r="D39" s="17" t="n"/>
-      <c r="E39" s="17" t="n"/>
-      <c r="F39" s="18" t="n"/>
+      <c r="D39" s="22" t="n"/>
+      <c r="E39" s="22" t="n"/>
+      <c r="F39" s="23" t="n"/>
     </row>
     <row r="40" ht="27" customHeight="1">
       <c r="A40" s="13" t="n"/>
@@ -1426,9 +1454,9 @@
           <t>При работе ручным шлифовальным (абразивным) инструментом, зачистке заусенцев:</t>
         </is>
       </c>
-      <c r="D48" s="17" t="n"/>
-      <c r="E48" s="17" t="n"/>
-      <c r="F48" s="18" t="n"/>
+      <c r="D48" s="22" t="n"/>
+      <c r="E48" s="22" t="n"/>
+      <c r="F48" s="23" t="n"/>
     </row>
     <row r="49" ht="40.5" customHeight="1">
       <c r="A49" s="12" t="n"/>
@@ -1486,9 +1514,9 @@
           <t>При выполнении работ в неотапливаемых помещениях, на открытом воздухе в холодный период года:</t>
         </is>
       </c>
-      <c r="D51" s="17" t="n"/>
-      <c r="E51" s="17" t="n"/>
-      <c r="F51" s="18" t="n"/>
+      <c r="D51" s="22" t="n"/>
+      <c r="E51" s="22" t="n"/>
+      <c r="F51" s="23" t="n"/>
     </row>
     <row r="52" ht="27" customHeight="1">
       <c r="A52" s="13" t="n"/>
@@ -1889,9 +1917,9 @@
           <t>При допуске к управлению подъёмными сооружениями (кран-балка, таль) с пола:</t>
         </is>
       </c>
-      <c r="D16" s="17" t="n"/>
-      <c r="E16" s="17" t="n"/>
-      <c r="F16" s="18" t="n"/>
+      <c r="D16" s="22" t="n"/>
+      <c r="E16" s="22" t="n"/>
+      <c r="F16" s="23" t="n"/>
     </row>
     <row r="17" ht="27" customHeight="1">
       <c r="A17" s="13" t="n"/>
@@ -2059,9 +2087,9 @@
           <t>При допуске к управлению подъёмными сооружениями (кран-балка, таль) с пола:</t>
         </is>
       </c>
-      <c r="D24" s="17" t="n"/>
-      <c r="E24" s="17" t="n"/>
-      <c r="F24" s="18" t="n"/>
+      <c r="D24" s="22" t="n"/>
+      <c r="E24" s="22" t="n"/>
+      <c r="F24" s="23" t="n"/>
     </row>
     <row r="25" ht="27" customHeight="1">
       <c r="A25" s="13" t="n"/>
@@ -2229,9 +2257,9 @@
           <t>При сверлении, зачистке, опиловке деталей из композиционных материалов и пластиков:</t>
         </is>
       </c>
-      <c r="D32" s="17" t="n"/>
-      <c r="E32" s="17" t="n"/>
-      <c r="F32" s="18" t="n"/>
+      <c r="D32" s="22" t="n"/>
+      <c r="E32" s="22" t="n"/>
+      <c r="F32" s="23" t="n"/>
     </row>
     <row r="33" ht="40.5" customHeight="1">
       <c r="A33" s="12" t="n"/>
@@ -2265,9 +2293,9 @@
           <t>При работе с клеями, герметиками, обезжиривающими составами:</t>
         </is>
       </c>
-      <c r="D34" s="17" t="n"/>
-      <c r="E34" s="17" t="n"/>
-      <c r="F34" s="18" t="n"/>
+      <c r="D34" s="22" t="n"/>
+      <c r="E34" s="22" t="n"/>
+      <c r="F34" s="23" t="n"/>
     </row>
     <row r="35" ht="27" customHeight="1">
       <c r="A35" s="12" t="n"/>
@@ -2349,9 +2377,9 @@
           <t>При допуске к управлению подъёмными сооружениями (кран-балка, таль) с пола:</t>
         </is>
       </c>
-      <c r="D38" s="17" t="n"/>
-      <c r="E38" s="17" t="n"/>
-      <c r="F38" s="18" t="n"/>
+      <c r="D38" s="22" t="n"/>
+      <c r="E38" s="22" t="n"/>
+      <c r="F38" s="23" t="n"/>
     </row>
     <row r="39" ht="27" customHeight="1">
       <c r="A39" s="13" t="n"/>
@@ -2861,9 +2889,9 @@
           <t>При раскрое и пошиве материалов, выделяющих волокна и пыль (стеклоткань, арамидные, огнестойкие ткани, препреги):</t>
         </is>
       </c>
-      <c r="D21" s="17" t="n"/>
-      <c r="E21" s="17" t="n"/>
-      <c r="F21" s="18" t="n"/>
+      <c r="D21" s="22" t="n"/>
+      <c r="E21" s="22" t="n"/>
+      <c r="F21" s="23" t="n"/>
     </row>
     <row r="22" ht="54" customHeight="1">
       <c r="A22" s="12" t="n"/>
@@ -3083,9 +3111,9 @@
           <t>При замене ножей, обслуживании режущей головки:</t>
         </is>
       </c>
-      <c r="D31" s="17" t="n"/>
-      <c r="E31" s="17" t="n"/>
-      <c r="F31" s="18" t="n"/>
+      <c r="D31" s="22" t="n"/>
+      <c r="E31" s="22" t="n"/>
+      <c r="F31" s="23" t="n"/>
     </row>
     <row r="32" ht="40.5" customHeight="1">
       <c r="A32" s="12" t="n"/>
@@ -3119,9 +3147,9 @@
           <t>При раскрое и пошиве материалов, выделяющих волокна и пыль (стеклоткань, арамидные, огнестойкие ткани, препреги):</t>
         </is>
       </c>
-      <c r="D33" s="17" t="n"/>
-      <c r="E33" s="17" t="n"/>
-      <c r="F33" s="18" t="n"/>
+      <c r="D33" s="22" t="n"/>
+      <c r="E33" s="22" t="n"/>
+      <c r="F33" s="23" t="n"/>
     </row>
     <row r="34" ht="54" customHeight="1">
       <c r="A34" s="12" t="n"/>
@@ -3903,6 +3931,1530 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:I53"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Подбор моделей СИЗ по прайсу спецодежды группы компаний (файл от 24.06) и стоимость на 1 работника в год (служебный расчет, не утверждается)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Участок / должность</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Позиция нормы</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Кол-во в год</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Модель из прайса</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>Поставщик / лист</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Цена за ед., руб.</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Сумма в год, руб.</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Комментарий (соответствие норме)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>Механический участок</t>
+        </is>
+      </c>
+      <c r="B4" s="22" t="n"/>
+      <c r="C4" s="22" t="n"/>
+      <c r="D4" s="22" t="n"/>
+      <c r="E4" s="22" t="n"/>
+      <c r="F4" s="22" t="n"/>
+      <c r="G4" s="22" t="n"/>
+      <c r="H4" s="22" t="n"/>
+      <c r="I4" s="23" t="n"/>
+    </row>
+    <row r="5" ht="40.5" customHeight="1">
+      <c r="A5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Мастер участка</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Костюм от механических воздействий (истирания) (Ми), муж.</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>Куртка летняя арт. 3308 «Дунай» + брюки арт. 3307 «Дунай»</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>Техноавиа / лист «АИ_СН»</t>
+        </is>
+      </c>
+      <c r="G5" s="18" t="n">
+        <v>10619.49</v>
+      </c>
+      <c r="H5" s="18">
+        <f>D5*G5</f>
+        <v/>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>По прайсу Казани модель заявлена «для защиты от механических воздействий и ОПЗ» - соответствует норме. Вариант с полукомбинезоном арт. 3312: 11 103,22 руб.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40.5" customHeight="1">
+      <c r="A6" s="12" t="n"/>
+      <c r="B6" s="12" t="n"/>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Обувь от механических воздействий (ударов) Мун200, муж.</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>Полуботинки с перфорацией «Комус Проф» с поликарбонатным подноском, арт. 2013431</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>Комус / лист «АИ_СН»</t>
+        </is>
+      </c>
+      <c r="G6" s="18" t="n">
+        <v>3490</v>
+      </c>
+      <c r="H6" s="18">
+        <f>D6*G6</f>
+        <v/>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>Дешевле: полуботинки «ЮКОН» арт. 50.387 (металлический подносок + проколозащитная стелька) - 3 091,20 руб., лист «Казань». Проверить маркировку Мун200</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="27" customHeight="1">
+      <c r="A7" s="12" t="n"/>
+      <c r="B7" s="12" t="n"/>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Головной убор от ОПЗ</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>Головной убор для защиты от общих производственных загрязнений</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>Профснаб / лист «Казань»</t>
+        </is>
+      </c>
+      <c r="G7" s="18" t="n">
+        <v>405</v>
+      </c>
+      <c r="H7" s="18">
+        <f>D7*G7</f>
+        <v/>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>Альтернатива: кепи-бейсболка «Оператор» арт. 8.022 - 576,84 руб.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" s="13" t="n"/>
+      <c r="B8" s="13" t="n"/>
+      <c r="C8" s="19" t="inlineStr">
+        <is>
+          <t>Итого по позициям с ценой (без условных позиций):</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="n"/>
+      <c r="E8" s="22" t="n"/>
+      <c r="F8" s="22" t="n"/>
+      <c r="G8" s="23" t="n"/>
+      <c r="H8" s="20">
+        <f>H5+H6+H7</f>
+        <v/>
+      </c>
+      <c r="I8" s="21" t="inlineStr">
+        <is>
+          <t>Без СИЗ, отсутствующих в прайсе (см. ниже)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="40.5" customHeight="1">
+      <c r="A9" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Оператор станков с программным управлением</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Костюм от механических воздействий (истирания) (Ми), муж.</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>Куртка летняя арт. 3308 «Дунай» + брюки арт. 3307 «Дунай»</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>Техноавиа / лист «АИ_СН»</t>
+        </is>
+      </c>
+      <c r="G9" s="18" t="n">
+        <v>10619.49</v>
+      </c>
+      <c r="H9" s="18">
+        <f>D9*G9</f>
+        <v/>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>По прайсу Казани модель заявлена «для защиты от механических воздействий и ОПЗ» - соответствует норме. Вариант с полукомбинезоном арт. 3312: 11 103,22 руб.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40.5" customHeight="1">
+      <c r="A10" s="12" t="n"/>
+      <c r="B10" s="12" t="n"/>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Обувь от механических воздействий (ударов) Мун200, муж.</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>Полуботинки с перфорацией «Комус Проф» с поликарбонатным подноском, арт. 2013431</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>Комус / лист «АИ_СН»</t>
+        </is>
+      </c>
+      <c r="G10" s="18" t="n">
+        <v>3490</v>
+      </c>
+      <c r="H10" s="18">
+        <f>D10*G10</f>
+        <v/>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t>Дешевле: полуботинки «ЮКОН» арт. 50.387 (металлический подносок + проколозащитная стелька) - 3 091,20 руб., лист «Казань». Проверить маркировку Мун200</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="27" customHeight="1">
+      <c r="A11" s="12" t="n"/>
+      <c r="B11" s="12" t="n"/>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Головной убор от ОПЗ</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>Головной убор для защиты от общих производственных загрязнений</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>Профснаб / лист «Казань»</t>
+        </is>
+      </c>
+      <c r="G11" s="18" t="n">
+        <v>405</v>
+      </c>
+      <c r="H11" s="18">
+        <f>D11*G11</f>
+        <v/>
+      </c>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t>Альтернатива: кепи-бейсболка «Оператор» арт. 8.022 - 576,84 руб.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="27" customHeight="1">
+      <c r="A12" s="12" t="n"/>
+      <c r="B12" s="12" t="n"/>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Куртка утепленная (условная позиция, 1 шт. на 2 года)</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>Куртка мужская зимняя арт. 2326 «Дунай»</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>Техноавиа / лист «АИ_СН»</t>
+        </is>
+      </c>
+      <c r="G12" s="18" t="n">
+        <v>9941.17</v>
+      </c>
+      <c r="H12" s="18">
+        <f>D12*G12</f>
+        <v/>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>Класс защиты Тн - по климатическому поясу. Условная позиция, в итог не включена</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" s="13" t="n"/>
+      <c r="B13" s="13" t="n"/>
+      <c r="C13" s="19" t="inlineStr">
+        <is>
+          <t>Итого по позициям с ценой (без условных позиций):</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="n"/>
+      <c r="E13" s="22" t="n"/>
+      <c r="F13" s="22" t="n"/>
+      <c r="G13" s="23" t="n"/>
+      <c r="H13" s="20">
+        <f>H9+H10+H11</f>
+        <v/>
+      </c>
+      <c r="I13" s="21" t="inlineStr">
+        <is>
+          <t>Без СИЗ, отсутствующих в прайсе (см. ниже)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="40.5" customHeight="1">
+      <c r="A14" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Токарь</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Костюм от механических воздействий (истирания) (Ми), муж.</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>Куртка летняя арт. 3308 «Дунай» + брюки арт. 3307 «Дунай»</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>Техноавиа / лист «АИ_СН»</t>
+        </is>
+      </c>
+      <c r="G14" s="18" t="n">
+        <v>10619.49</v>
+      </c>
+      <c r="H14" s="18">
+        <f>D14*G14</f>
+        <v/>
+      </c>
+      <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t>По прайсу Казани модель заявлена «для защиты от механических воздействий и ОПЗ» - соответствует норме. Вариант с полукомбинезоном арт. 3312: 11 103,22 руб.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="40.5" customHeight="1">
+      <c r="A15" s="12" t="n"/>
+      <c r="B15" s="12" t="n"/>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Обувь от механических воздействий (ударов) Мун200, муж.</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>Полуботинки с перфорацией «Комус Проф» с поликарбонатным подноском, арт. 2013431</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>Комус / лист «АИ_СН»</t>
+        </is>
+      </c>
+      <c r="G15" s="18" t="n">
+        <v>3490</v>
+      </c>
+      <c r="H15" s="18">
+        <f>D15*G15</f>
+        <v/>
+      </c>
+      <c r="I15" s="8" t="inlineStr">
+        <is>
+          <t>Дешевле: полуботинки «ЮКОН» арт. 50.387 (металлический подносок + проколозащитная стелька) - 3 091,20 руб., лист «Казань». Проверить маркировку Мун200</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="27" customHeight="1">
+      <c r="A16" s="12" t="n"/>
+      <c r="B16" s="12" t="n"/>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Головной убор от ОПЗ</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>Головной убор для защиты от общих производственных загрязнений</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>Профснаб / лист «Казань»</t>
+        </is>
+      </c>
+      <c r="G16" s="18" t="n">
+        <v>405</v>
+      </c>
+      <c r="H16" s="18">
+        <f>D16*G16</f>
+        <v/>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>Альтернатива: кепи-бейсболка «Оператор» арт. 8.022 - 576,84 руб.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" s="13" t="n"/>
+      <c r="B17" s="13" t="n"/>
+      <c r="C17" s="19" t="inlineStr">
+        <is>
+          <t>Итого по позициям с ценой (без условных позиций):</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="n"/>
+      <c r="E17" s="22" t="n"/>
+      <c r="F17" s="22" t="n"/>
+      <c r="G17" s="23" t="n"/>
+      <c r="H17" s="20">
+        <f>H14+H15+H16</f>
+        <v/>
+      </c>
+      <c r="I17" s="21" t="inlineStr">
+        <is>
+          <t>Без СИЗ, отсутствующих в прайсе (см. ниже)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="40.5" customHeight="1">
+      <c r="A18" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Слесарь механосборочных работ</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Костюм от механических воздействий (истирания) (Ми), муж.</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>Куртка летняя арт. 3308 «Дунай» + брюки арт. 3307 «Дунай»</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>Техноавиа / лист «АИ_СН»</t>
+        </is>
+      </c>
+      <c r="G18" s="18" t="n">
+        <v>10619.49</v>
+      </c>
+      <c r="H18" s="18">
+        <f>D18*G18</f>
+        <v/>
+      </c>
+      <c r="I18" s="8" t="inlineStr">
+        <is>
+          <t>По прайсу Казани модель заявлена «для защиты от механических воздействий и ОПЗ» - соответствует норме. Вариант с полукомбинезоном арт. 3312: 11 103,22 руб.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="40.5" customHeight="1">
+      <c r="A19" s="12" t="n"/>
+      <c r="B19" s="12" t="n"/>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Обувь от механических воздействий (ударов) Мун200, муж.</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>Полуботинки с перфорацией «Комус Проф» с поликарбонатным подноском, арт. 2013431</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>Комус / лист «АИ_СН»</t>
+        </is>
+      </c>
+      <c r="G19" s="18" t="n">
+        <v>3490</v>
+      </c>
+      <c r="H19" s="18">
+        <f>D19*G19</f>
+        <v/>
+      </c>
+      <c r="I19" s="8" t="inlineStr">
+        <is>
+          <t>Дешевле: полуботинки «ЮКОН» арт. 50.387 (металлический подносок + проколозащитная стелька) - 3 091,20 руб., лист «Казань». Проверить маркировку Мун200</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="27" customHeight="1">
+      <c r="A20" s="12" t="n"/>
+      <c r="B20" s="12" t="n"/>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Головной убор от ОПЗ</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>Головной убор для защиты от общих производственных загрязнений</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>Профснаб / лист «Казань»</t>
+        </is>
+      </c>
+      <c r="G20" s="18" t="n">
+        <v>405</v>
+      </c>
+      <c r="H20" s="18">
+        <f>D20*G20</f>
+        <v/>
+      </c>
+      <c r="I20" s="8" t="inlineStr">
+        <is>
+          <t>Альтернатива: кепи-бейсболка «Оператор» арт. 8.022 - 576,84 руб.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="27" customHeight="1">
+      <c r="A21" s="12" t="n"/>
+      <c r="B21" s="12" t="n"/>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Куртка утепленная (условная позиция, 1 шт. на 2 года)</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>Куртка мужская зимняя арт. 2326 «Дунай»</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>Техноавиа / лист «АИ_СН»</t>
+        </is>
+      </c>
+      <c r="G21" s="18" t="n">
+        <v>9941.17</v>
+      </c>
+      <c r="H21" s="18">
+        <f>D21*G21</f>
+        <v/>
+      </c>
+      <c r="I21" s="8" t="inlineStr">
+        <is>
+          <t>Класс защиты Тн - по климатическому поясу. Условная позиция, в итог не включена</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" s="13" t="n"/>
+      <c r="B22" s="13" t="n"/>
+      <c r="C22" s="19" t="inlineStr">
+        <is>
+          <t>Итого по позициям с ценой (без условных позиций):</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="n"/>
+      <c r="E22" s="22" t="n"/>
+      <c r="F22" s="22" t="n"/>
+      <c r="G22" s="23" t="n"/>
+      <c r="H22" s="20">
+        <f>H18+H19+H20</f>
+        <v/>
+      </c>
+      <c r="I22" s="21" t="inlineStr">
+        <is>
+          <t>Без СИЗ, отсутствующих в прайсе (см. ниже)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" s="17" t="inlineStr">
+        <is>
+          <t>Сборочный участок</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="n"/>
+      <c r="C23" s="22" t="n"/>
+      <c r="D23" s="22" t="n"/>
+      <c r="E23" s="22" t="n"/>
+      <c r="F23" s="22" t="n"/>
+      <c r="G23" s="22" t="n"/>
+      <c r="H23" s="22" t="n"/>
+      <c r="I23" s="23" t="n"/>
+    </row>
+    <row r="24" ht="40.5" customHeight="1">
+      <c r="A24" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Начальник участка</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Костюм от механических воздействий (истирания) (Ми), муж.</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>Куртка летняя арт. 3308 «Дунай» + брюки арт. 3307 «Дунай»</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>Техноавиа / лист «АИ_СН»</t>
+        </is>
+      </c>
+      <c r="G24" s="18" t="n">
+        <v>10619.49</v>
+      </c>
+      <c r="H24" s="18">
+        <f>D24*G24</f>
+        <v/>
+      </c>
+      <c r="I24" s="8" t="inlineStr">
+        <is>
+          <t>По прайсу Казани модель заявлена «для защиты от механических воздействий и ОПЗ» - соответствует норме. Вариант с полукомбинезоном арт. 3312: 11 103,22 руб.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="40.5" customHeight="1">
+      <c r="A25" s="12" t="n"/>
+      <c r="B25" s="12" t="n"/>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>Обувь от механических воздействий (ударов) Мун200, муж.</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>Полуботинки с перфорацией «Комус Проф» с поликарбонатным подноском, арт. 2013431</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>Комус / лист «АИ_СН»</t>
+        </is>
+      </c>
+      <c r="G25" s="18" t="n">
+        <v>3490</v>
+      </c>
+      <c r="H25" s="18">
+        <f>D25*G25</f>
+        <v/>
+      </c>
+      <c r="I25" s="8" t="inlineStr">
+        <is>
+          <t>Дешевле: полуботинки «ЮКОН» арт. 50.387 (металлический подносок + проколозащитная стелька) - 3 091,20 руб., лист «Казань». Проверить маркировку Мун200</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" s="13" t="n"/>
+      <c r="B26" s="13" t="n"/>
+      <c r="C26" s="19" t="inlineStr">
+        <is>
+          <t>Итого по позициям с ценой (без условных позиций):</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="n"/>
+      <c r="E26" s="22" t="n"/>
+      <c r="F26" s="22" t="n"/>
+      <c r="G26" s="23" t="n"/>
+      <c r="H26" s="20">
+        <f>H24+H25</f>
+        <v/>
+      </c>
+      <c r="I26" s="21" t="inlineStr">
+        <is>
+          <t>Без СИЗ, отсутствующих в прайсе (см. ниже)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="40.5" customHeight="1">
+      <c r="A27" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Мастер участка</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>Костюм от механических воздействий (истирания) (Ми), муж.</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>Куртка летняя арт. 3308 «Дунай» + брюки арт. 3307 «Дунай»</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>Техноавиа / лист «АИ_СН»</t>
+        </is>
+      </c>
+      <c r="G27" s="18" t="n">
+        <v>10619.49</v>
+      </c>
+      <c r="H27" s="18">
+        <f>D27*G27</f>
+        <v/>
+      </c>
+      <c r="I27" s="8" t="inlineStr">
+        <is>
+          <t>По прайсу Казани модель заявлена «для защиты от механических воздействий и ОПЗ» - соответствует норме. Вариант с полукомбинезоном арт. 3312: 11 103,22 руб.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="40.5" customHeight="1">
+      <c r="A28" s="12" t="n"/>
+      <c r="B28" s="12" t="n"/>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Обувь от механических воздействий (ударов) Мун200, муж.</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>Полуботинки с перфорацией «Комус Проф» с поликарбонатным подноском, арт. 2013431</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>Комус / лист «АИ_СН»</t>
+        </is>
+      </c>
+      <c r="G28" s="18" t="n">
+        <v>3490</v>
+      </c>
+      <c r="H28" s="18">
+        <f>D28*G28</f>
+        <v/>
+      </c>
+      <c r="I28" s="8" t="inlineStr">
+        <is>
+          <t>Дешевле: полуботинки «ЮКОН» арт. 50.387 (металлический подносок + проколозащитная стелька) - 3 091,20 руб., лист «Казань». Проверить маркировку Мун200</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="27" customHeight="1">
+      <c r="A29" s="12" t="n"/>
+      <c r="B29" s="12" t="n"/>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>Головной убор от ОПЗ</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>Головной убор для защиты от общих производственных загрязнений</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>Профснаб / лист «Казань»</t>
+        </is>
+      </c>
+      <c r="G29" s="18" t="n">
+        <v>405</v>
+      </c>
+      <c r="H29" s="18">
+        <f>D29*G29</f>
+        <v/>
+      </c>
+      <c r="I29" s="8" t="inlineStr">
+        <is>
+          <t>Альтернатива: кепи-бейсболка «Оператор» арт. 8.022 - 576,84 руб.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" s="13" t="n"/>
+      <c r="B30" s="13" t="n"/>
+      <c r="C30" s="19" t="inlineStr">
+        <is>
+          <t>Итого по позициям с ценой (без условных позиций):</t>
+        </is>
+      </c>
+      <c r="D30" s="22" t="n"/>
+      <c r="E30" s="22" t="n"/>
+      <c r="F30" s="22" t="n"/>
+      <c r="G30" s="23" t="n"/>
+      <c r="H30" s="20">
+        <f>H27+H28+H29</f>
+        <v/>
+      </c>
+      <c r="I30" s="21" t="inlineStr">
+        <is>
+          <t>Без СИЗ, отсутствующих в прайсе (см. ниже)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="40.5" customHeight="1">
+      <c r="A31" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Слесарь-сборщик</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>Костюм от механических воздействий (истирания) (Ми), муж.</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>Куртка летняя арт. 3308 «Дунай» + брюки арт. 3307 «Дунай»</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>Техноавиа / лист «АИ_СН»</t>
+        </is>
+      </c>
+      <c r="G31" s="18" t="n">
+        <v>10619.49</v>
+      </c>
+      <c r="H31" s="18">
+        <f>D31*G31</f>
+        <v/>
+      </c>
+      <c r="I31" s="8" t="inlineStr">
+        <is>
+          <t>По прайсу Казани модель заявлена «для защиты от механических воздействий и ОПЗ» - соответствует норме. Вариант с полукомбинезоном арт. 3312: 11 103,22 руб.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="40.5" customHeight="1">
+      <c r="A32" s="12" t="n"/>
+      <c r="B32" s="12" t="n"/>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>Обувь от механических воздействий (ударов) Мун200, муж.</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>Полуботинки с перфорацией «Комус Проф» с поликарбонатным подноском, арт. 2013431</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>Комус / лист «АИ_СН»</t>
+        </is>
+      </c>
+      <c r="G32" s="18" t="n">
+        <v>3490</v>
+      </c>
+      <c r="H32" s="18">
+        <f>D32*G32</f>
+        <v/>
+      </c>
+      <c r="I32" s="8" t="inlineStr">
+        <is>
+          <t>Дешевле: полуботинки «ЮКОН» арт. 50.387 (металлический подносок + проколозащитная стелька) - 3 091,20 руб., лист «Казань». Проверить маркировку Мун200</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="27" customHeight="1">
+      <c r="A33" s="12" t="n"/>
+      <c r="B33" s="12" t="n"/>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>Головной убор от ОПЗ</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>Головной убор для защиты от общих производственных загрязнений</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>Профснаб / лист «Казань»</t>
+        </is>
+      </c>
+      <c r="G33" s="18" t="n">
+        <v>405</v>
+      </c>
+      <c r="H33" s="18">
+        <f>D33*G33</f>
+        <v/>
+      </c>
+      <c r="I33" s="8" t="inlineStr">
+        <is>
+          <t>Альтернатива: кепи-бейсболка «Оператор» арт. 8.022 - 576,84 руб.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" s="13" t="n"/>
+      <c r="B34" s="13" t="n"/>
+      <c r="C34" s="19" t="inlineStr">
+        <is>
+          <t>Итого по позициям с ценой (без условных позиций):</t>
+        </is>
+      </c>
+      <c r="D34" s="22" t="n"/>
+      <c r="E34" s="22" t="n"/>
+      <c r="F34" s="22" t="n"/>
+      <c r="G34" s="23" t="n"/>
+      <c r="H34" s="20">
+        <f>H31+H32+H33</f>
+        <v/>
+      </c>
+      <c r="I34" s="21" t="inlineStr">
+        <is>
+          <t>Без СИЗ, отсутствующих в прайсе (см. ниже)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" s="17" t="inlineStr">
+        <is>
+          <t>Швейный участок</t>
+        </is>
+      </c>
+      <c r="B35" s="22" t="n"/>
+      <c r="C35" s="22" t="n"/>
+      <c r="D35" s="22" t="n"/>
+      <c r="E35" s="22" t="n"/>
+      <c r="F35" s="22" t="n"/>
+      <c r="G35" s="22" t="n"/>
+      <c r="H35" s="22" t="n"/>
+      <c r="I35" s="23" t="n"/>
+    </row>
+    <row r="36" ht="40.5" customHeight="1">
+      <c r="A36" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>Мастер участка (жен.)</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>Халат/костюм от ОПЗ и истирания (мастер швейного участка, жен.)</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>Халат женский «Бьянка-2» арт. 4.804</t>
+        </is>
+      </c>
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t>Техноавиа / лист «Казань»</t>
+        </is>
+      </c>
+      <c r="G36" s="18" t="n">
+        <v>3782.12</v>
+      </c>
+      <c r="H36" s="18">
+        <f>D36*G36</f>
+        <v/>
+      </c>
+      <c r="I36" s="8" t="inlineStr">
+        <is>
+          <t>Модель из раздела «медицинская одежда»: проверить, что это СИЗ с декларацией ТР ТС 019/2011 (З, Ми). Если нет - заменить на халат/костюм с защитными свойствами</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="40.5" customHeight="1">
+      <c r="A37" s="12" t="n"/>
+      <c r="B37" s="12" t="n"/>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>Обувь от механических воздействий (истирания) Ми, жен. (швейный участок)</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>Ботинки женские летние арт. 50649</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>Техноавиа / лист «АИ_СН»</t>
+        </is>
+      </c>
+      <c r="G37" s="18" t="n">
+        <v>1619.16</v>
+      </c>
+      <c r="H37" s="18">
+        <f>D37*G37</f>
+        <v/>
+      </c>
+      <c r="I37" s="8" t="inlineStr">
+        <is>
+          <t>Проверить маркировку Ми. Туфли-сабо «Леон медикал» (Казань, 4 905,44 руб.) - медицинская обувь, требованиям нормы не соответствуют без декларации ТР ТС 019/2011</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" s="12" t="n"/>
+      <c r="B38" s="12" t="n"/>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>Головной убор от ОПЗ (швейный участок)</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t>Косынка арт. 8.051</t>
+        </is>
+      </c>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>Техноавиа / лист «Казань»</t>
+        </is>
+      </c>
+      <c r="G38" s="18" t="n">
+        <v>107.64</v>
+      </c>
+      <c r="H38" s="18">
+        <f>D38*G38</f>
+        <v/>
+      </c>
+      <c r="I38" s="8" t="inlineStr"/>
+    </row>
+    <row r="39" ht="15" customHeight="1">
+      <c r="A39" s="13" t="n"/>
+      <c r="B39" s="13" t="n"/>
+      <c r="C39" s="19" t="inlineStr">
+        <is>
+          <t>Итого по позициям с ценой (без условных позиций):</t>
+        </is>
+      </c>
+      <c r="D39" s="22" t="n"/>
+      <c r="E39" s="22" t="n"/>
+      <c r="F39" s="22" t="n"/>
+      <c r="G39" s="23" t="n"/>
+      <c r="H39" s="20">
+        <f>H36+H37+H38</f>
+        <v/>
+      </c>
+      <c r="I39" s="21" t="inlineStr">
+        <is>
+          <t>Без СИЗ, отсутствующих в прайсе (см. ниже)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="27" customHeight="1">
+      <c r="A40" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>Специалист по пошиву (жен.)</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>Костюм от механических воздействий (истирания) (Ми), жен.</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>Куртка летняя арт. 3310 + брюки арт. 3311</t>
+        </is>
+      </c>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t>Техноавиа / лист «АИ_СН»</t>
+        </is>
+      </c>
+      <c r="G40" s="18" t="n">
+        <v>10318.76</v>
+      </c>
+      <c r="H40" s="18">
+        <f>D40*G40</f>
+        <v/>
+      </c>
+      <c r="I40" s="8" t="inlineStr">
+        <is>
+          <t>Проверить в декларации ТР ТС 019/2011 наличие защитных свойств Ми, З</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="40.5" customHeight="1">
+      <c r="A41" s="12" t="n"/>
+      <c r="B41" s="12" t="n"/>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>Обувь от механических воздействий (истирания) Ми, жен. (швейный участок)</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>Ботинки женские летние арт. 50649</t>
+        </is>
+      </c>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>Техноавиа / лист «АИ_СН»</t>
+        </is>
+      </c>
+      <c r="G41" s="18" t="n">
+        <v>1619.16</v>
+      </c>
+      <c r="H41" s="18">
+        <f>D41*G41</f>
+        <v/>
+      </c>
+      <c r="I41" s="8" t="inlineStr">
+        <is>
+          <t>Проверить маркировку Ми. Туфли-сабо «Леон медикал» (Казань, 4 905,44 руб.) - медицинская обувь, требованиям нормы не соответствуют без декларации ТР ТС 019/2011</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="15" customHeight="1">
+      <c r="A42" s="12" t="n"/>
+      <c r="B42" s="12" t="n"/>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>Головной убор от ОПЗ (швейный участок)</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t>Косынка арт. 8.051</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t>Техноавиа / лист «Казань»</t>
+        </is>
+      </c>
+      <c r="G42" s="18" t="n">
+        <v>107.64</v>
+      </c>
+      <c r="H42" s="18">
+        <f>D42*G42</f>
+        <v/>
+      </c>
+      <c r="I42" s="8" t="inlineStr"/>
+    </row>
+    <row r="43" ht="15" customHeight="1">
+      <c r="A43" s="13" t="n"/>
+      <c r="B43" s="13" t="n"/>
+      <c r="C43" s="19" t="inlineStr">
+        <is>
+          <t>Итого по позициям с ценой (без условных позиций):</t>
+        </is>
+      </c>
+      <c r="D43" s="22" t="n"/>
+      <c r="E43" s="22" t="n"/>
+      <c r="F43" s="22" t="n"/>
+      <c r="G43" s="23" t="n"/>
+      <c r="H43" s="20">
+        <f>H40+H41+H42</f>
+        <v/>
+      </c>
+      <c r="I43" s="21" t="inlineStr">
+        <is>
+          <t>Без СИЗ, отсутствующих в прайсе (см. ниже)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="27" customHeight="1">
+      <c r="A44" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>Оператор станков с ПУ, раскройный комплекс (жен.)</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>Костюм от механических воздействий (истирания) (Ми), жен.</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t>Куртка летняя арт. 3310 + брюки арт. 3311</t>
+        </is>
+      </c>
+      <c r="F44" s="8" t="inlineStr">
+        <is>
+          <t>Техноавиа / лист «АИ_СН»</t>
+        </is>
+      </c>
+      <c r="G44" s="18" t="n">
+        <v>10318.76</v>
+      </c>
+      <c r="H44" s="18">
+        <f>D44*G44</f>
+        <v/>
+      </c>
+      <c r="I44" s="8" t="inlineStr">
+        <is>
+          <t>Проверить в декларации ТР ТС 019/2011 наличие защитных свойств Ми, З</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="27" customHeight="1">
+      <c r="A45" s="12" t="n"/>
+      <c r="B45" s="12" t="n"/>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>Обувь от механических воздействий (ударов) Мун200, жен.</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" s="8" t="inlineStr">
+        <is>
+          <t>Ботинки женские летние арт. 50319</t>
+        </is>
+      </c>
+      <c r="F45" s="8" t="inlineStr">
+        <is>
+          <t>Техноавиа / лист «АИ_СН»</t>
+        </is>
+      </c>
+      <c r="G45" s="18" t="n">
+        <v>5077.64</v>
+      </c>
+      <c r="H45" s="18">
+        <f>D45*G45</f>
+        <v/>
+      </c>
+      <c r="I45" s="8" t="inlineStr">
+        <is>
+          <t>Проверить наличие защитного подноска 200 Дж</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="15" customHeight="1">
+      <c r="A46" s="12" t="n"/>
+      <c r="B46" s="12" t="n"/>
+      <c r="C46" s="8" t="inlineStr">
+        <is>
+          <t>Головной убор от ОПЗ (швейный участок)</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" s="8" t="inlineStr">
+        <is>
+          <t>Косынка арт. 8.051</t>
+        </is>
+      </c>
+      <c r="F46" s="8" t="inlineStr">
+        <is>
+          <t>Техноавиа / лист «Казань»</t>
+        </is>
+      </c>
+      <c r="G46" s="18" t="n">
+        <v>107.64</v>
+      </c>
+      <c r="H46" s="18">
+        <f>D46*G46</f>
+        <v/>
+      </c>
+      <c r="I46" s="8" t="inlineStr"/>
+    </row>
+    <row r="47" ht="15" customHeight="1">
+      <c r="A47" s="13" t="n"/>
+      <c r="B47" s="13" t="n"/>
+      <c r="C47" s="19" t="inlineStr">
+        <is>
+          <t>Итого по позициям с ценой (без условных позиций):</t>
+        </is>
+      </c>
+      <c r="D47" s="22" t="n"/>
+      <c r="E47" s="22" t="n"/>
+      <c r="F47" s="22" t="n"/>
+      <c r="G47" s="23" t="n"/>
+      <c r="H47" s="20">
+        <f>H44+H45+H46</f>
+        <v/>
+      </c>
+      <c r="I47" s="21" t="inlineStr">
+        <is>
+          <t>Без СИЗ, отсутствующих в прайсе (см. ниже)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="15" customHeight="1"/>
+    <row r="49" ht="15" customHeight="1">
+      <c r="A49" s="14" t="inlineStr">
+        <is>
+          <t>Выводы:</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="27" customHeight="1">
+      <c r="A50" s="15" t="inlineStr">
+        <is>
+          <t>1. В прайсе группы есть только спецодежда, спецобувь и головные уборы. Для остальных СИЗ из норм нужен отдельный запрос цен: Перчатки (Ми / Ми, Мп / от порезов); Очки защитные открытые и закрытые; Щиток защитный лицевой; Фильтрующие полумаски FFP1/FFP2; Противошумные вкладыши/наушники; Каска защитная; Фартук; Перчатки химстойкие (нитриловые); Дерматологические СИЗ и смывающие средства.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="15" customHeight="1">
+      <c r="A51" s="15" t="inlineStr">
+        <is>
+          <t>2. На швейном участке Казани выдаются флисовая куртка «Софт-2», брюки «Лагонда», туфли-сабо «Леон медикал», поло. Это не СИЗ по ЕТН п.5145 «Швея» (костюм и обувь с защитой Ми). Для АИ СН этот комплект как образец не использовать без проверки деклараций.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="15" customHeight="1">
+      <c r="A52" s="15" t="inlineStr">
+        <is>
+          <t>3. Перед закупкой по каждой модели проверить декларацию/сертификат ТР ТС 019/2011 (реестр ФГИС Росаккредитации) и маркировку защитных свойств (Ми, З, Мун200, Тн).</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="15" customHeight="1">
+      <c r="A53" s="15" t="inlineStr">
+        <is>
+          <t>4. Цены - из прайса (без учета изменения цен после 24.06). Для работников другого пола - подставить соответствующую модель.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="39">
+    <mergeCell ref="A36:A39"/>
+    <mergeCell ref="A18:A22"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="B31:B34"/>
+    <mergeCell ref="B9:B13"/>
+    <mergeCell ref="B24:B26"/>
+    <mergeCell ref="B27:B30"/>
+    <mergeCell ref="A50:I50"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="A9:A13"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="A23:I23"/>
+    <mergeCell ref="A24:A26"/>
+    <mergeCell ref="A53:I53"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A35:I35"/>
+    <mergeCell ref="A52:I52"/>
+    <mergeCell ref="A27:A30"/>
+    <mergeCell ref="B44:B47"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="B40:B43"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A5:A8"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="B5:B8"/>
+    <mergeCell ref="B18:B22"/>
+    <mergeCell ref="B36:B39"/>
+    <mergeCell ref="A44:A47"/>
+    <mergeCell ref="A49:I49"/>
+    <mergeCell ref="A51:I51"/>
+    <mergeCell ref="A31:A34"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="A40:A43"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/documents/SIZ_2026/Normy_SIZ_AI_specnaznacheniya_2026.xlsx
+++ b/documents/SIZ_2026/Normy_SIZ_AI_specnaznacheniya_2026.xlsx
@@ -549,7 +549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.3" customWidth="1" min="1" max="1"/>
@@ -1182,7 +1182,7 @@
           <t>1 шт. на 1 год</t>
         </is>
       </c>
-      <c r="F36" s="13" t="n"/>
+      <c r="F36" s="11" t="n"/>
     </row>
     <row r="37" ht="54" customHeight="1">
       <c r="A37" s="13" t="n"/>
@@ -1194,194 +1194,194 @@
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>Противоаэрозольные, противоаэрозольные с дополнительной защитой от паров и газов средства индивидуальной защиты органов дыхания с фильтрующей лицевой частью - фильтрующие полумаски одноразовые, класс защиты не ниже FFP1</t>
+          <t>Изолирующая лицевая часть - полумаска многоразовая для использования со сменными фильтрами</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t>1 шт. на смену (247 шт. на 1 год)</t>
-        </is>
-      </c>
-      <c r="F37" s="11" t="n"/>
-    </row>
-    <row r="38" ht="27" customHeight="1">
+          <t>1 шт. на 1 год</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>Приложение №1 ЕТН, п.4872 (замена фильтрующей полумаски на равноценное СИЗ); Приложение №2 ЕТН, п.7.3.1; п.16 Правил (приказ №766н)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="40.5" customHeight="1">
       <c r="A38" s="13" t="n"/>
       <c r="B38" s="13" t="n"/>
-      <c r="C38" s="8" t="inlineStr">
-        <is>
-          <t>Средства индивидуальной защиты органа слуха</t>
-        </is>
-      </c>
+      <c r="C38" s="8" t="n"/>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>Противошумные вкладыши (беруши) многоразовые</t>
+          <t>Сменные фильтры противоаэрозольные, класс защиты не ниже P1 (при образовании паров СОЖ - противогазоаэрозольные комбинированные)</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr">
         <is>
-          <t>12 пар на 1 год (1 пара на 1 месяц)</t>
-        </is>
-      </c>
-      <c r="F38" s="8" t="inlineStr">
-        <is>
-          <t>Приложение №2 ЕТН, п.10.1.1 (опасность идентифицирована по результатам ОПР)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="15" customHeight="1">
+          <t>1 комплект на 5 смен (50 комплектов на 1 год)</t>
+        </is>
+      </c>
+      <c r="F38" s="11" t="n"/>
+    </row>
+    <row r="39" ht="27" customHeight="1">
       <c r="A39" s="13" t="n"/>
       <c r="B39" s="13" t="n"/>
-      <c r="C39" s="8" t="n"/>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>Средства индивидуальной защиты органа слуха</t>
+        </is>
+      </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>или Противошумные наушники</t>
+          <t>Противошумные вкладыши (беруши) многоразовые</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
         <is>
-          <t>1 шт. на 1 год</t>
-        </is>
-      </c>
-      <c r="F39" s="11" t="n"/>
+          <t>12 пар на 1 год (1 пара на 1 месяц)</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t>Приложение №2 ЕТН, п.10.1.1 (опасность идентифицирована по результатам ОПР)</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" s="13" t="n"/>
       <c r="B40" s="13" t="n"/>
-      <c r="C40" s="12" t="inlineStr">
-        <is>
-          <t>При обработке деталей с образованием сливной стружки, при работе на станке без защитного экрана:</t>
-        </is>
-      </c>
-      <c r="D40" s="17" t="n"/>
-      <c r="E40" s="17" t="n"/>
-      <c r="F40" s="18" t="n"/>
-    </row>
-    <row r="41" ht="40.5" customHeight="1">
+      <c r="C40" s="8" t="n"/>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>или Противошумные наушники</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="inlineStr">
+        <is>
+          <t>1 шт. на 1 год</t>
+        </is>
+      </c>
+      <c r="F40" s="11" t="n"/>
+    </row>
+    <row r="41" ht="15" customHeight="1">
       <c r="A41" s="13" t="n"/>
       <c r="B41" s="13" t="n"/>
-      <c r="C41" s="8" t="inlineStr">
-        <is>
-          <t>Средства индивидуальной защиты глаз и лица от механических воздействий</t>
-        </is>
-      </c>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t>Щиток защитный лицевой от механических воздействий (ударов твердых частиц)</t>
-        </is>
-      </c>
-      <c r="E41" s="9" t="inlineStr">
-        <is>
-          <t>1 шт. на 1 год</t>
-        </is>
-      </c>
-      <c r="F41" s="8" t="inlineStr">
-        <is>
-          <t>Приложение №2 ЕТН, п.1.21.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="15" customHeight="1">
+      <c r="C41" s="12" t="inlineStr">
+        <is>
+          <t>При обработке деталей с образованием сливной стружки, при работе на станке без защитного экрана:</t>
+        </is>
+      </c>
+      <c r="D41" s="17" t="n"/>
+      <c r="E41" s="17" t="n"/>
+      <c r="F41" s="18" t="n"/>
+    </row>
+    <row r="42" ht="40.5" customHeight="1">
       <c r="A42" s="13" t="n"/>
       <c r="B42" s="13" t="n"/>
-      <c r="C42" s="12" t="inlineStr">
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>Средства индивидуальной защиты глаз и лица от механических воздействий</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>Щиток защитный лицевой от механических воздействий (ударов твердых частиц)</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="inlineStr">
+        <is>
+          <t>1 шт. на 1 год</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t>Приложение №2 ЕТН, п.1.21.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="15" customHeight="1">
+      <c r="A43" s="13" t="n"/>
+      <c r="B43" s="13" t="n"/>
+      <c r="C43" s="12" t="inlineStr">
         <is>
           <t>При допуске к управлению подъёмными сооружениями (кран-балка, таль) с пола:</t>
         </is>
       </c>
-      <c r="D42" s="17" t="n"/>
-      <c r="E42" s="17" t="n"/>
-      <c r="F42" s="18" t="n"/>
-    </row>
-    <row r="43" ht="27" customHeight="1">
-      <c r="A43" s="11" t="n"/>
-      <c r="B43" s="11" t="n"/>
-      <c r="C43" s="8" t="inlineStr">
+      <c r="D43" s="17" t="n"/>
+      <c r="E43" s="17" t="n"/>
+      <c r="F43" s="18" t="n"/>
+    </row>
+    <row r="44" ht="27" customHeight="1">
+      <c r="A44" s="11" t="n"/>
+      <c r="B44" s="11" t="n"/>
+      <c r="C44" s="8" t="inlineStr">
         <is>
           <t>Средства индивидуальной защиты головы от механических воздействий</t>
         </is>
       </c>
-      <c r="D43" s="8" t="inlineStr">
+      <c r="D44" s="8" t="inlineStr">
         <is>
           <t>Каска защитная</t>
         </is>
       </c>
-      <c r="E43" s="9" t="inlineStr">
+      <c r="E44" s="9" t="inlineStr">
         <is>
           <t>1 шт. на 2 года</t>
         </is>
       </c>
-      <c r="F43" s="8" t="inlineStr">
+      <c r="F44" s="8" t="inlineStr">
         <is>
           <t>Приложение №2 ЕТН, п.1.3.1</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="15" customHeight="1">
-      <c r="A44" s="6" t="n">
+    <row r="45" ht="15" customHeight="1">
+      <c r="A45" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B44" s="7" t="inlineStr">
+      <c r="B45" s="7" t="inlineStr">
         <is>
           <t>Слесарь механосборочных работ</t>
         </is>
       </c>
-      <c r="C44" s="8" t="inlineStr">
+      <c r="C45" s="8" t="inlineStr">
         <is>
           <t>Одежда специальная защитная</t>
         </is>
       </c>
-      <c r="D44" s="8" t="inlineStr">
+      <c r="D45" s="8" t="inlineStr">
         <is>
           <t>Костюм для защиты от механических воздействий (истирания) (Ми)</t>
         </is>
       </c>
-      <c r="E44" s="9" t="inlineStr">
+      <c r="E45" s="9" t="inlineStr">
         <is>
           <t>1 шт. на 1 год</t>
         </is>
       </c>
-      <c r="F44" s="8" t="inlineStr">
+      <c r="F45" s="8" t="inlineStr">
         <is>
           <t>Приложение №1 ЕТН, п.4516</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="40.5" customHeight="1">
-      <c r="A45" s="13" t="n"/>
-      <c r="B45" s="13" t="n"/>
-      <c r="C45" s="8" t="inlineStr">
-        <is>
-          <t>Средства защиты ног</t>
-        </is>
-      </c>
-      <c r="D45" s="8" t="inlineStr">
-        <is>
-          <t>Обувь специальная для защиты от механических воздействий (ударов в носочной части 200 Дж), с маслобензостойкой противоскользящей подошвой (Мун200)</t>
-        </is>
-      </c>
-      <c r="E45" s="9" t="inlineStr">
-        <is>
-          <t>1 пара на 1 год</t>
-        </is>
-      </c>
-      <c r="F45" s="13" t="n"/>
-    </row>
-    <row r="46" ht="15" customHeight="1">
+    <row r="46" ht="40.5" customHeight="1">
       <c r="A46" s="13" t="n"/>
       <c r="B46" s="13" t="n"/>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Средства защиты рук</t>
+          <t>Средства защиты ног</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Перчатки для защиты от механических воздействий (истирания) (Ми)</t>
+          <t>Обувь специальная для защиты от механических воздействий (ударов в носочной части 200 Дж), с маслобензостойкой противоскользящей подошвой (Мун200)</t>
         </is>
       </c>
       <c r="E46" s="9" t="inlineStr">
         <is>
-          <t>12 пар на 1 год</t>
+          <t>1 пара на 1 год</t>
         </is>
       </c>
       <c r="F46" s="13" t="n"/>
@@ -1391,17 +1391,17 @@
       <c r="B47" s="13" t="n"/>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>Средства защиты головы</t>
+          <t>Средства защиты рук</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>Головной убор для защиты от общих производственных загрязнений</t>
+          <t>Перчатки для защиты от механических воздействий (истирания) (Ми)</t>
         </is>
       </c>
       <c r="E47" s="9" t="inlineStr">
         <is>
-          <t>1 шт. на 1 год</t>
+          <t>12 пар на 1 год</t>
         </is>
       </c>
       <c r="F47" s="13" t="n"/>
@@ -1409,268 +1409,276 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" s="13" t="n"/>
       <c r="B48" s="13" t="n"/>
-      <c r="C48" s="8" t="n"/>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>Средства защиты головы</t>
+        </is>
+      </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Каска защитная от механических воздействий</t>
+          <t>Головной убор для защиты от общих производственных загрязнений</t>
         </is>
       </c>
       <c r="E48" s="9" t="inlineStr">
         <is>
-          <t>1 шт. на 2 года</t>
+          <t>1 шт. на 1 год</t>
         </is>
       </c>
       <c r="F48" s="13" t="n"/>
     </row>
-    <row r="49" ht="27" customHeight="1">
+    <row r="49" ht="15" customHeight="1">
       <c r="A49" s="13" t="n"/>
       <c r="B49" s="13" t="n"/>
-      <c r="C49" s="8" t="inlineStr">
-        <is>
-          <t>Средства защиты глаз</t>
-        </is>
-      </c>
+      <c r="C49" s="8" t="n"/>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>Очки защитные от механических воздействий, в том числе с покрытием от запотевания</t>
+          <t>Каска защитная от механических воздействий</t>
         </is>
       </c>
       <c r="E49" s="9" t="inlineStr">
         <is>
-          <t>1 шт. на 1 год</t>
-        </is>
-      </c>
-      <c r="F49" s="11" t="n"/>
+          <t>1 шт. на 2 года</t>
+        </is>
+      </c>
+      <c r="F49" s="13" t="n"/>
     </row>
     <row r="50" ht="27" customHeight="1">
       <c r="A50" s="13" t="n"/>
       <c r="B50" s="13" t="n"/>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Средства индивидуальной защиты органа слуха</t>
+          <t>Средства защиты глаз</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>Противошумные вкладыши (беруши) многоразовые</t>
+          <t>Очки защитные от механических воздействий, в том числе с покрытием от запотевания</t>
         </is>
       </c>
       <c r="E50" s="9" t="inlineStr">
         <is>
-          <t>12 пар на 1 год (1 пара на 1 месяц)</t>
-        </is>
-      </c>
-      <c r="F50" s="8" t="inlineStr">
-        <is>
-          <t>Приложение №2 ЕТН, п.10.1.1 (опасность идентифицирована по результатам ОПР)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="15" customHeight="1">
+          <t>1 шт. на 1 год</t>
+        </is>
+      </c>
+      <c r="F50" s="11" t="n"/>
+    </row>
+    <row r="51" ht="27" customHeight="1">
       <c r="A51" s="13" t="n"/>
       <c r="B51" s="13" t="n"/>
-      <c r="C51" s="8" t="n"/>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>Средства индивидуальной защиты органа слуха</t>
+        </is>
+      </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>или Противошумные наушники</t>
+          <t>Противошумные вкладыши (беруши) многоразовые</t>
         </is>
       </c>
       <c r="E51" s="9" t="inlineStr">
         <is>
-          <t>1 шт. на 1 год</t>
-        </is>
-      </c>
-      <c r="F51" s="11" t="n"/>
+          <t>12 пар на 1 год (1 пара на 1 месяц)</t>
+        </is>
+      </c>
+      <c r="F51" s="8" t="inlineStr">
+        <is>
+          <t>Приложение №2 ЕТН, п.10.1.1 (опасность идентифицирована по результатам ОПР)</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="15" customHeight="1">
       <c r="A52" s="13" t="n"/>
       <c r="B52" s="13" t="n"/>
-      <c r="C52" s="12" t="inlineStr">
-        <is>
-          <t>При работе ручным шлифовальным (абразивным) инструментом, зачистке заусенцев:</t>
-        </is>
-      </c>
-      <c r="D52" s="17" t="n"/>
-      <c r="E52" s="17" t="n"/>
-      <c r="F52" s="18" t="n"/>
-    </row>
-    <row r="53" ht="40.5" customHeight="1">
+      <c r="C52" s="8" t="n"/>
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t>или Противошумные наушники</t>
+        </is>
+      </c>
+      <c r="E52" s="9" t="inlineStr">
+        <is>
+          <t>1 шт. на 1 год</t>
+        </is>
+      </c>
+      <c r="F52" s="11" t="n"/>
+    </row>
+    <row r="53" ht="15" customHeight="1">
       <c r="A53" s="13" t="n"/>
       <c r="B53" s="13" t="n"/>
-      <c r="C53" s="8" t="inlineStr">
-        <is>
-          <t>Средства индивидуальной защиты глаз и лица от механических воздействий</t>
-        </is>
-      </c>
-      <c r="D53" s="8" t="inlineStr">
-        <is>
-          <t>Щиток защитный лицевой от механических воздействий (ударов твердых частиц)</t>
-        </is>
-      </c>
-      <c r="E53" s="9" t="inlineStr">
-        <is>
-          <t>1 шт. на 1 год</t>
-        </is>
-      </c>
-      <c r="F53" s="8" t="inlineStr">
-        <is>
-          <t>Приложение №2 ЕТН, п.1.24.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="54" customHeight="1">
+      <c r="C53" s="12" t="inlineStr">
+        <is>
+          <t>При работе ручным шлифовальным (абразивным) инструментом, зачистке заусенцев:</t>
+        </is>
+      </c>
+      <c r="D53" s="17" t="n"/>
+      <c r="E53" s="17" t="n"/>
+      <c r="F53" s="18" t="n"/>
+    </row>
+    <row r="54" ht="40.5" customHeight="1">
       <c r="A54" s="13" t="n"/>
       <c r="B54" s="13" t="n"/>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Средства индивидуальной защиты органов дыхания фильтрующего типа противоаэрозольные</t>
+          <t>Средства индивидуальной защиты глаз и лица от механических воздействий</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>Противоаэрозольные средства индивидуальной защиты органов дыхания с фильтрующей лицевой частью - фильтрующие полумаски одноразовые, класс защиты не ниже FFP2</t>
+          <t>Щиток защитный лицевой от механических воздействий (ударов твердых частиц)</t>
         </is>
       </c>
       <c r="E54" s="9" t="inlineStr">
         <is>
-          <t>1 шт. на смену выполнения указанных работ, не более 247 шт. на 1 год</t>
+          <t>1 шт. на 1 год</t>
         </is>
       </c>
       <c r="F54" s="8" t="inlineStr">
         <is>
-          <t>Приложение №2 ЕТН, п.7.1.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="15" customHeight="1">
+          <t>Приложение №2 ЕТН, п.1.24.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="54" customHeight="1">
       <c r="A55" s="13" t="n"/>
       <c r="B55" s="13" t="n"/>
-      <c r="C55" s="12" t="inlineStr">
+      <c r="C55" s="8" t="inlineStr">
+        <is>
+          <t>Средства индивидуальной защиты органов дыхания фильтрующего типа противоаэрозольные</t>
+        </is>
+      </c>
+      <c r="D55" s="8" t="inlineStr">
+        <is>
+          <t>Противоаэрозольные средства индивидуальной защиты органов дыхания с фильтрующей лицевой частью - фильтрующие полумаски одноразовые, класс защиты не ниже FFP2</t>
+        </is>
+      </c>
+      <c r="E55" s="9" t="inlineStr">
+        <is>
+          <t>1 шт. на смену выполнения указанных работ, не более 247 шт. на 1 год</t>
+        </is>
+      </c>
+      <c r="F55" s="8" t="inlineStr">
+        <is>
+          <t>Приложение №2 ЕТН, п.7.1.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="15" customHeight="1">
+      <c r="A56" s="13" t="n"/>
+      <c r="B56" s="13" t="n"/>
+      <c r="C56" s="12" t="inlineStr">
         <is>
           <t>При выполнении работ в неотапливаемых помещениях, на открытом воздухе в холодный период года:</t>
         </is>
       </c>
-      <c r="D55" s="17" t="n"/>
-      <c r="E55" s="17" t="n"/>
-      <c r="F55" s="18" t="n"/>
-    </row>
-    <row r="56" ht="27" customHeight="1">
-      <c r="A56" s="11" t="n"/>
-      <c r="B56" s="11" t="n"/>
-      <c r="C56" s="8" t="inlineStr">
+      <c r="D56" s="17" t="n"/>
+      <c r="E56" s="17" t="n"/>
+      <c r="F56" s="18" t="n"/>
+    </row>
+    <row r="57" ht="27" customHeight="1">
+      <c r="A57" s="11" t="n"/>
+      <c r="B57" s="11" t="n"/>
+      <c r="C57" s="8" t="inlineStr">
         <is>
           <t>Одежда специальная для защиты от пониженных температур</t>
         </is>
       </c>
-      <c r="D56" s="8" t="inlineStr">
+      <c r="D57" s="8" t="inlineStr">
         <is>
           <t>Куртка утепленная для защиты от пониженных температур (класс защиты Тн по климатическому поясу места нахождения предприятия)</t>
         </is>
       </c>
-      <c r="E56" s="9" t="inlineStr">
+      <c r="E57" s="9" t="inlineStr">
         <is>
           <t>1 шт. на 2 года</t>
         </is>
       </c>
-      <c r="F56" s="8" t="inlineStr">
+      <c r="F57" s="8" t="inlineStr">
         <is>
           <t>Приложение №2 ЕТН, п.4.7.1</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="15" customHeight="1"/>
-    <row r="58" ht="15" customHeight="1">
-      <c r="B58" s="14" t="inlineStr">
+    <row r="58" ht="15" customHeight="1"/>
+    <row r="59" ht="15" customHeight="1">
+      <c r="B59" s="14" t="inlineStr">
         <is>
           <t>Примечания:</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="30" customHeight="1">
-      <c r="B59" s="15" t="inlineStr">
-        <is>
-          <t>1. Выдаются СИЗ, имеющие действующий сертификат или декларацию соответствия ТР ТС 019/2011 (п.7 Правил, приказ №766н), с защитными свойствами, указанными в графе 4.</t>
         </is>
       </c>
     </row>
     <row r="60" ht="30" customHeight="1">
       <c r="B60" s="15" t="inlineStr">
         <is>
-          <t>2. СИЗ органа слуха установлены по результатам ОПР (опасность «повышенный уровень шума», п.10.1 Приложения №2 ЕТН). СОУТ по фактору «шум» не проводилась: после проведения СОУТ (измерений) эффективность СИЗ (SNR) подтверждается по фактическому уровню шума, нормы актуализируются (п.19 Правил).</t>
+          <t>1. Выдаются СИЗ, имеющие действующий сертификат или декларацию соответствия ТР ТС 019/2011 (п.7 Правил, приказ №766н), с защитными свойствами, указанными в графе 4.</t>
         </is>
       </c>
     </row>
     <row r="61" ht="30" customHeight="1">
       <c r="B61" s="15" t="inlineStr">
         <is>
-          <t>3. Работа в перчатках на станках с вращающимися частями (шпиндель, патрон, заготовка) запрещена (Правила по охране труда при обработке металлов, приказ Минтруда России №887н). Перчатки применяются при установке/снятии заготовок, уборке стружки, слесарных операциях.</t>
+          <t>2. СИЗ органа слуха установлены по результатам ОПР (опасность «повышенный уровень шума», п.10.1 Приложения №2 ЕТН). СОУТ по фактору «шум» не проводилась: после проведения СОУТ (измерений) эффективность СИЗ (SNR) подтверждается по фактическому уровню шума, нормы актуализируются (п.19 Правил).</t>
         </is>
       </c>
     </row>
     <row r="62" ht="30" customHeight="1">
       <c r="B62" s="15" t="inlineStr">
         <is>
-          <t>4. СИЗ по строкам «При …» выдаются работникам, фактически выполняющим указанные работы (перечень утверждается распоряжением по участку).</t>
+          <t>3. Работа в перчатках на станках с вращающимися частями (шпиндель, патрон, заготовка) запрещена (Правила по охране труда при обработке металлов, приказ Минтруда России №887н). Перчатки применяются при установке/снятии заготовок, уборке стружки, слесарных операциях.</t>
         </is>
       </c>
     </row>
     <row r="63" ht="30" customHeight="1">
       <c r="B63" s="15" t="inlineStr">
         <is>
-          <t>5. Количество одноразовых СИЗ органов дыхания рассчитано на 247 рабочих смен (производственный календарь 2026 г., пятидневная рабочая неделя).</t>
+          <t>4. СИЗ по строкам «При …» выдаются работникам, фактически выполняющим указанные работы (перечень утверждается распоряжением по участку).</t>
         </is>
       </c>
     </row>
     <row r="64" ht="30" customHeight="1">
       <c r="B64" s="15" t="inlineStr">
         <is>
+          <t>5. Количество одноразовых СИЗ органов дыхания и сменных фильтров рассчитано на 247 рабочих смен (производственный календарь 2026 г., пятидневная рабочая неделя).</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="30" customHeight="1">
+      <c r="B65" s="15" t="inlineStr">
+        <is>
           <t>6. Нормы подлежат сверке с результатами СОУТ и ОПР и актуализации при их изменении (п.14, п.19 Правил, приказ №766н).</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="15" customHeight="1"/>
-    <row r="66" ht="15" customHeight="1">
-      <c r="B66" s="4" t="inlineStr">
+    <row r="66" ht="15" customHeight="1"/>
+    <row r="67" ht="15" customHeight="1">
+      <c r="B67" s="4" t="inlineStr">
         <is>
           <t>Разработал:</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="32" customHeight="1">
-      <c r="B67" s="16" t="inlineStr">
+    <row r="68" ht="32" customHeight="1">
+      <c r="B68" s="16" t="inlineStr">
         <is>
           <t>Начальник отдела охраны труда и промышленной безопасности</t>
         </is>
       </c>
-      <c r="D67" s="16" t="inlineStr">
+      <c r="D68" s="16" t="inlineStr">
         <is>
           <t>________________ / ____________</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="15" customHeight="1">
-      <c r="B68" s="4" t="inlineStr">
+    <row r="69" ht="15" customHeight="1">
+      <c r="B69" s="4" t="inlineStr">
         <is>
           <t>Согласовано:</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="32" customHeight="1">
-      <c r="B69" s="16" t="inlineStr">
-        <is>
-          <t>Директор по производству</t>
-        </is>
-      </c>
-      <c r="D69" s="16" t="inlineStr">
-        <is>
-          <t>________________ / ____________</t>
         </is>
       </c>
     </row>
     <row r="70" ht="32" customHeight="1">
       <c r="B70" s="16" t="inlineStr">
         <is>
-          <t>Начальник участка</t>
+          <t>Директор по производству</t>
         </is>
       </c>
       <c r="D70" s="16" t="inlineStr">
@@ -1682,7 +1690,7 @@
     <row r="71" ht="32" customHeight="1">
       <c r="B71" s="16" t="inlineStr">
         <is>
-          <t>Мастер участка</t>
+          <t>Начальник участка</t>
         </is>
       </c>
       <c r="D71" s="16" t="inlineStr">
@@ -1694,58 +1702,71 @@
     <row r="72" ht="32" customHeight="1">
       <c r="B72" s="16" t="inlineStr">
         <is>
+          <t>Мастер участка</t>
+        </is>
+      </c>
+      <c r="D72" s="16" t="inlineStr">
+        <is>
+          <t>________________ / ____________</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="32" customHeight="1">
+      <c r="B73" s="16" t="inlineStr">
+        <is>
           <t>Представитель выборного органа первичной профсоюзной организации (при наличии)</t>
         </is>
       </c>
-      <c r="D72" s="16" t="inlineStr">
+      <c r="D73" s="16" t="inlineStr">
         <is>
           <t>________________ / ____________</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="41">
+  <mergeCells count="42">
     <mergeCell ref="D2:F2"/>
-    <mergeCell ref="C52:F52"/>
+    <mergeCell ref="F32:F36"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="B62:F62"/>
     <mergeCell ref="B72:C72"/>
-    <mergeCell ref="F44:F49"/>
     <mergeCell ref="B59:F59"/>
+    <mergeCell ref="A45:A57"/>
     <mergeCell ref="C19:F19"/>
     <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B58:F58"/>
     <mergeCell ref="C28:F28"/>
     <mergeCell ref="B70:C70"/>
+    <mergeCell ref="C53:F53"/>
+    <mergeCell ref="F45:F50"/>
     <mergeCell ref="A21:A31"/>
     <mergeCell ref="F21:F24"/>
     <mergeCell ref="F26:F27"/>
+    <mergeCell ref="F51:F52"/>
     <mergeCell ref="D4:F4"/>
     <mergeCell ref="F17:F18"/>
-    <mergeCell ref="B44:B56"/>
     <mergeCell ref="B60:F60"/>
     <mergeCell ref="C30:F30"/>
-    <mergeCell ref="B67:C67"/>
     <mergeCell ref="D3:F3"/>
-    <mergeCell ref="B32:B43"/>
     <mergeCell ref="B61:F61"/>
-    <mergeCell ref="C42:F42"/>
-    <mergeCell ref="F50:F51"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="F32:F37"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="A32:A44"/>
     <mergeCell ref="D5:F5"/>
-    <mergeCell ref="F38:F39"/>
+    <mergeCell ref="F37:F38"/>
+    <mergeCell ref="F39:F40"/>
+    <mergeCell ref="C41:F41"/>
     <mergeCell ref="D1:F1"/>
-    <mergeCell ref="C55:F55"/>
     <mergeCell ref="B13:B20"/>
-    <mergeCell ref="A44:A56"/>
-    <mergeCell ref="C40:F40"/>
+    <mergeCell ref="B45:B57"/>
+    <mergeCell ref="B65:F65"/>
     <mergeCell ref="C9:F9"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="C56:F56"/>
     <mergeCell ref="B64:F64"/>
+    <mergeCell ref="C43:F43"/>
     <mergeCell ref="B63:F63"/>
     <mergeCell ref="B21:B31"/>
+    <mergeCell ref="B32:B44"/>
     <mergeCell ref="A13:A20"/>
-    <mergeCell ref="A32:A43"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -2564,7 +2585,7 @@
     <row r="50" ht="30" customHeight="1">
       <c r="B50" s="15" t="inlineStr">
         <is>
-          <t>5. Количество одноразовых СИЗ органов дыхания рассчитано на 247 рабочих смен (производственный календарь 2026 г., пятидневная рабочая неделя).</t>
+          <t>5. Количество одноразовых СИЗ органов дыхания и сменных фильтров рассчитано на 247 рабочих смен (производственный календарь 2026 г., пятидневная рабочая неделя).</t>
         </is>
       </c>
     </row>
@@ -3183,7 +3204,7 @@
     <row r="33" ht="30" customHeight="1">
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>5. Количество одноразовых СИЗ органов дыхания рассчитано на 247 рабочих смен (производственный календарь 2026 г., пятидневная рабочая неделя).</t>
+          <t>5. Количество одноразовых СИЗ органов дыхания и сменных фильтров рассчитано на 247 рабочих смен (производственный календарь 2026 г., пятидневная рабочая неделя).</t>
         </is>
       </c>
     </row>
@@ -3941,7 +3962,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="40.5" customHeight="1">
+    <row r="6" ht="67.5" customHeight="1">
       <c r="A6" s="9" t="n">
         <v>3</v>
       </c>
@@ -3957,7 +3978,7 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>СИЗ органа слуха, щиток (сливная стружка), каска (кран-балка). Полумаски FFP1 по ЕТН «до износа» - конкретизировано: 1 шт. на смену</t>
+          <t>СИЗ органа слуха, щиток (сливная стружка), каска (кран-балка). Фильтрующие полумаски по ЕТН заменены на многоразовую полумаску (1 шт. на 1 год) со сменными фильтрами P1 (50 комплектов на 1 год) - равноценная защита, п.16 Правил 766н, Прил. №2 п.7.3.1</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
@@ -4162,7 +4183,7 @@
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>- Приказ Минтруда России от 29.10.2021 №767н (ЕТН): Приложение №1 пп.3283, 4516, 4562, 4872, 5145; Приложение №2 пп.1.3.1, 1.21.1, 1.24.1, 1.28, 2.1.1, 2.1.2, 4.7.1, 6.5.1, 6.9, 7.1.1, 7.1.2, 10.1.1; Приложение №3 Табл. 1, 2.</t>
+          <t>- Приказ Минтруда России от 29.10.2021 №767н (ЕТН): Приложение №1 пп.3283, 4516, 4562, 4872, 5145; Приложение №2 пп.1.3.1, 1.21.1, 1.24.1, 1.28, 2.1.1, 2.1.2, 4.7.1, 6.5.1, 6.9, 7.1.1, 7.1.2, 7.3.1, 10.1.1; Приложение №3 Табл. 1, 2.</t>
         </is>
       </c>
     </row>

--- a/documents/SIZ_2026/Normy_SIZ_AI_specnaznacheniya_2026.xlsx
+++ b/documents/SIZ_2026/Normy_SIZ_AI_specnaznacheniya_2026.xlsx
@@ -549,7 +549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.3" customWidth="1" min="1" max="1"/>
@@ -618,7 +618,7 @@
       </c>
     </row>
     <row r="10" ht="15" customHeight="1"/>
-    <row r="11" ht="64" customHeight="1">
+    <row r="11" ht="67.5" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
           <t>№ п/п</t>
@@ -626,7 +626,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Должность работника</t>
+          <t>Наименование профессии (должности)</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -641,12 +641,12 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Нормы выдачи на год (период), единицы измерения (штуки, пары, комплекты)</t>
+          <t>Нормы выдачи с указанием периодичности выдачи, количества на период, единицы измерения (штуки, пары, комплекты, г, мл.)</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Основание выдачи СИЗ (пункты Единых типовых норм (ЕТН), правил по охране труда и иных документов)</t>
+          <t>Основание выдачи СИЗ (пункты Единых типовых норм, правил по охране труда и иных документов)</t>
         </is>
       </c>
     </row>
@@ -670,7 +670,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" ht="40.5" customHeight="1">
+    <row r="13" ht="54" customHeight="1">
       <c r="A13" s="6" t="n">
         <v>1</v>
       </c>
@@ -696,7 +696,7 @@
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>Приложение №2 ЕТН, п.2.1.1; п.18 Правил обеспечения работников СИЗ (приказ Минтруда №766н)</t>
+          <t>Приложение №2 ЕТН, п.2.1.1; Приложение №1 ЕТН, пп.3283, 4872, 4516 (по виду контролируемых работ); п.18 Правил обеспечения работников СИЗ (приказ Минтруда №766н)</t>
         </is>
       </c>
     </row>
@@ -724,41 +724,41 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="27" customHeight="1">
+    <row r="15" ht="40.5" customHeight="1">
       <c r="A15" s="13" t="n"/>
       <c r="B15" s="13" t="n"/>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Средства защиты головы</t>
+          <t>Средства защиты рук</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>Головной убор для защиты от общих производственных загрязнений (кепка, бейсболка)</t>
+          <t>Перчатки для защиты от механических воздействий (истирания) (Ми)</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>1 шт. на 1 год</t>
+          <t>12 пар на 1 год</t>
         </is>
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>Приложение №2 ЕТН, п.2.1.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="40.5" customHeight="1">
+          <t>Приложение №1 ЕТН (по виду контролируемых работ); п.18 Правил обеспечения работников СИЗ (приказ Минтруда №766н)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="27" customHeight="1">
       <c r="A16" s="13" t="n"/>
       <c r="B16" s="13" t="n"/>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Средства индивидуальной защиты глаз и лица от механических воздействий</t>
+          <t>Средства защиты головы</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Очки защитные открытые от механических воздействий, класс оптики 1, прочность не ниже F, с покрытием от запотевания</t>
+          <t>Головной убор для защиты от общих производственных загрязнений (кепка, бейсболка)</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
@@ -768,152 +768,156 @@
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>Приложение №2 ЕТН, п.1.24.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="27" customHeight="1">
+          <t>Приложение №2 ЕТН, п.2.1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="40.5" customHeight="1">
       <c r="A17" s="13" t="n"/>
       <c r="B17" s="13" t="n"/>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Средства индивидуальной защиты органа слуха</t>
+          <t>Средства индивидуальной защиты глаз и лица от механических воздействий</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>Противошумные вкладыши (беруши) многоразовые</t>
+          <t>Очки защитные открытые от механических воздействий, класс оптики 1, прочность не ниже F, с покрытием от запотевания</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>12 пар на 1 год (1 пара на 1 месяц)</t>
+          <t>1 шт. на 1 год</t>
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t>Приложение №2 ЕТН, п.10.1.1 (опасность идентифицирована по результатам ОПР)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
+          <t>Приложение №2 ЕТН, п.1.24.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="27" customHeight="1">
       <c r="A18" s="13" t="n"/>
       <c r="B18" s="13" t="n"/>
-      <c r="C18" s="8" t="n"/>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Средства индивидуальной защиты органа слуха</t>
+        </is>
+      </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>или Противошумные наушники</t>
+          <t>Противошумные вкладыши (беруши) многоразовые</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>1 шт. на 1 год</t>
-        </is>
-      </c>
-      <c r="F18" s="11" t="n"/>
+          <t>12 пар на 1 год (1 пара на 1 месяц)</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>Приложение №2 ЕТН, п.10.1.1 (опасность идентифицирована по результатам ОПР)</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" s="13" t="n"/>
       <c r="B19" s="13" t="n"/>
-      <c r="C19" s="12" t="inlineStr">
+      <c r="C19" s="8" t="n"/>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>или Противошумные наушники</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>1 шт. на 1 год</t>
+        </is>
+      </c>
+      <c r="F19" s="11" t="n"/>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" s="13" t="n"/>
+      <c r="B20" s="13" t="n"/>
+      <c r="C20" s="12" t="inlineStr">
         <is>
           <t>При допуске к управлению подъёмными сооружениями (кран-балка, таль) с пола:</t>
         </is>
       </c>
-      <c r="D19" s="17" t="n"/>
-      <c r="E19" s="17" t="n"/>
-      <c r="F19" s="18" t="n"/>
-    </row>
-    <row r="20" ht="27" customHeight="1">
-      <c r="A20" s="11" t="n"/>
-      <c r="B20" s="11" t="n"/>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="D20" s="17" t="n"/>
+      <c r="E20" s="17" t="n"/>
+      <c r="F20" s="18" t="n"/>
+    </row>
+    <row r="21" ht="27" customHeight="1">
+      <c r="A21" s="11" t="n"/>
+      <c r="B21" s="11" t="n"/>
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>Средства индивидуальной защиты головы от механических воздействий</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t>Каска защитная</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="E21" s="9" t="inlineStr">
         <is>
           <t>1 шт. на 2 года</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="F21" s="8" t="inlineStr">
         <is>
           <t>Приложение №2 ЕТН, п.1.3.1</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="27" customHeight="1">
-      <c r="A21" s="6" t="n">
+    <row r="22" ht="27" customHeight="1">
+      <c r="A22" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>Оператор станков с программным управлением</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>Одежда специальная защитная</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>Костюм для защиты от механических воздействий (истирания) (Ми)</t>
         </is>
       </c>
-      <c r="E21" s="9" t="inlineStr">
+      <c r="E22" s="9" t="inlineStr">
         <is>
           <t>1 шт. на 1 год</t>
         </is>
       </c>
-      <c r="F21" s="8" t="inlineStr">
+      <c r="F22" s="8" t="inlineStr">
         <is>
           <t>Приложение №1 ЕТН, п.3283</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="40.5" customHeight="1">
-      <c r="A22" s="13" t="n"/>
-      <c r="B22" s="13" t="n"/>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>Средства защиты ног</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>Обувь специальная для защиты от механических воздействий (ударов в носочной части 200 Дж), с маслобензостойкой противоскользящей подошвой (Мун200)</t>
-        </is>
-      </c>
-      <c r="E22" s="9" t="inlineStr">
-        <is>
-          <t>1 пара на 1 год</t>
-        </is>
-      </c>
-      <c r="F22" s="13" t="n"/>
-    </row>
-    <row r="23" ht="15" customHeight="1">
+    <row r="23" ht="40.5" customHeight="1">
       <c r="A23" s="13" t="n"/>
       <c r="B23" s="13" t="n"/>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Средства защиты рук</t>
+          <t>Средства защиты ног</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>Перчатки для защиты от механических воздействий (истирания) (Ми)</t>
+          <t>Обувь специальная для защиты от механических воздействий (ударов в носочной части 200 Дж), с маслобензостойкой противоскользящей подошвой (Мун200)</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>12 пар на 1 год</t>
+          <t>1 пара на 1 год</t>
         </is>
       </c>
       <c r="F23" s="13" t="n"/>
@@ -923,32 +927,32 @@
       <c r="B24" s="13" t="n"/>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Средства защиты головы</t>
+          <t>Средства защиты рук</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Головной убор для защиты от общих производственных загрязнений</t>
+          <t>Перчатки для защиты от механических воздействий (истирания) (Ми)</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>1 шт. на 1 год</t>
-        </is>
-      </c>
-      <c r="F24" s="11" t="n"/>
-    </row>
-    <row r="25" ht="40.5" customHeight="1">
+          <t>12 пар на 1 год</t>
+        </is>
+      </c>
+      <c r="F24" s="13" t="n"/>
+    </row>
+    <row r="25" ht="15" customHeight="1">
       <c r="A25" s="13" t="n"/>
       <c r="B25" s="13" t="n"/>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>Средства индивидуальной защиты глаз и лица от механических воздействий</t>
+          <t>Средства защиты головы</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>Очки защитные открытые от механических воздействий, класс оптики 1, прочность не ниже F, с покрытием от запотевания</t>
+          <t>Головной убор для защиты от общих производственных загрязнений</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
@@ -956,225 +960,225 @@
           <t>1 шт. на 1 год</t>
         </is>
       </c>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>Приложение №2 ЕТН, п.1.24.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="27" customHeight="1">
+      <c r="F25" s="11" t="n"/>
+    </row>
+    <row r="26" ht="40.5" customHeight="1">
       <c r="A26" s="13" t="n"/>
       <c r="B26" s="13" t="n"/>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Средства индивидуальной защиты органа слуха</t>
+          <t>Средства индивидуальной защиты глаз и лица от механических воздействий</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Противошумные вкладыши (беруши) многоразовые</t>
+          <t>Очки защитные открытые от механических воздействий, класс оптики 1, прочность не ниже F, с покрытием от запотевания</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>12 пар на 1 год (1 пара на 1 месяц)</t>
+          <t>1 шт. на 1 год</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr">
         <is>
-          <t>Приложение №2 ЕТН, п.10.1.1 (опасность идентифицирована по результатам ОПР)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1">
+          <t>Приложение №2 ЕТН, п.1.24.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="27" customHeight="1">
       <c r="A27" s="13" t="n"/>
       <c r="B27" s="13" t="n"/>
-      <c r="C27" s="8" t="n"/>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>Средства индивидуальной защиты органа слуха</t>
+        </is>
+      </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>или Противошумные наушники</t>
+          <t>Противошумные вкладыши (беруши) многоразовые</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>1 шт. на 1 год</t>
-        </is>
-      </c>
-      <c r="F27" s="11" t="n"/>
+          <t>12 пар на 1 год (1 пара на 1 месяц)</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>Приложение №2 ЕТН, п.10.1.1 (опасность идентифицирована по результатам ОПР)</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" s="13" t="n"/>
       <c r="B28" s="13" t="n"/>
-      <c r="C28" s="12" t="inlineStr">
-        <is>
-          <t>При допуске к управлению подъёмными сооружениями (кран-балка, таль) с пола:</t>
-        </is>
-      </c>
-      <c r="D28" s="17" t="n"/>
-      <c r="E28" s="17" t="n"/>
-      <c r="F28" s="18" t="n"/>
-    </row>
-    <row r="29" ht="27" customHeight="1">
+      <c r="C28" s="8" t="n"/>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>или Противошумные наушники</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>1 шт. на 1 год</t>
+        </is>
+      </c>
+      <c r="F28" s="11" t="n"/>
+    </row>
+    <row r="29" ht="15" customHeight="1">
       <c r="A29" s="13" t="n"/>
       <c r="B29" s="13" t="n"/>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>Средства индивидуальной защиты головы от механических воздействий</t>
-        </is>
-      </c>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>Каска защитная</t>
-        </is>
-      </c>
-      <c r="E29" s="9" t="inlineStr">
-        <is>
-          <t>1 шт. на 2 года</t>
-        </is>
-      </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t>Приложение №2 ЕТН, п.1.3.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1">
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>При допуске к управлению подъёмными сооружениями (кран-балка, таль) с пола:</t>
+        </is>
+      </c>
+      <c r="D29" s="17" t="n"/>
+      <c r="E29" s="17" t="n"/>
+      <c r="F29" s="18" t="n"/>
+    </row>
+    <row r="30" ht="27" customHeight="1">
       <c r="A30" s="13" t="n"/>
       <c r="B30" s="13" t="n"/>
-      <c r="C30" s="12" t="inlineStr">
-        <is>
-          <t>При выполнении работ в неотапливаемых помещениях, на открытом воздухе в холодный период года:</t>
-        </is>
-      </c>
-      <c r="D30" s="17" t="n"/>
-      <c r="E30" s="17" t="n"/>
-      <c r="F30" s="18" t="n"/>
-    </row>
-    <row r="31" ht="27" customHeight="1">
-      <c r="A31" s="11" t="n"/>
-      <c r="B31" s="11" t="n"/>
-      <c r="C31" s="8" t="inlineStr">
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>Средства индивидуальной защиты головы от механических воздействий</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>Каска защитная</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>1 шт. на 2 года</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>Приложение №2 ЕТН, п.1.3.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" s="13" t="n"/>
+      <c r="B31" s="13" t="n"/>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>При кратковременной работе в неотапливаемых помещениях, на открытом воздухе в холодный период года (погрузка, выгрузка, перемещение между зданиями):</t>
+        </is>
+      </c>
+      <c r="D31" s="17" t="n"/>
+      <c r="E31" s="17" t="n"/>
+      <c r="F31" s="18" t="n"/>
+    </row>
+    <row r="32" ht="40.5" customHeight="1">
+      <c r="A32" s="11" t="n"/>
+      <c r="B32" s="11" t="n"/>
+      <c r="C32" s="8" t="inlineStr">
         <is>
           <t>Одежда специальная для защиты от пониженных температур</t>
         </is>
       </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>Куртка утепленная для защиты от пониженных температур (класс защиты Тн по климатическому поясу места нахождения предприятия)</t>
-        </is>
-      </c>
-      <c r="E31" s="9" t="inlineStr">
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>Куртка утепленная для защиты от пониженных температур, 1 класс защиты (II климатический пояс); выдается на холодный период года с последующей сдачей на хранение</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="inlineStr">
         <is>
           <t>1 шт. на 2 года</t>
         </is>
       </c>
-      <c r="F31" s="8" t="inlineStr">
-        <is>
-          <t>Приложение №2 ЕТН, п.4.7.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="A32" s="6" t="n">
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>Приложение №2 ЕТН, п.4.7.1; пп.48, 50, Приложение №4 Правил (приказ №766н)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>Токарь</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr">
+      <c r="C33" s="8" t="inlineStr">
         <is>
           <t>Одежда специальная защитная</t>
         </is>
       </c>
-      <c r="D32" s="8" t="inlineStr">
+      <c r="D33" s="8" t="inlineStr">
         <is>
           <t>Костюм для защиты от механических воздействий (истирания) (Ми)</t>
         </is>
       </c>
-      <c r="E32" s="9" t="inlineStr">
+      <c r="E33" s="9" t="inlineStr">
         <is>
           <t>1 шт. на 1 год</t>
         </is>
       </c>
-      <c r="F32" s="8" t="inlineStr">
+      <c r="F33" s="8" t="inlineStr">
         <is>
           <t>Приложение №1 ЕТН, п.4872</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="40.5" customHeight="1">
-      <c r="A33" s="13" t="n"/>
-      <c r="B33" s="13" t="n"/>
-      <c r="C33" s="8" t="inlineStr">
-        <is>
-          <t>Средства защиты ног</t>
-        </is>
-      </c>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>Обувь специальная для защиты от механических воздействий (ударов в носочной части 200 Дж), с маслобензостойкой противоскользящей подошвой (Мун200)</t>
-        </is>
-      </c>
-      <c r="E33" s="9" t="inlineStr">
-        <is>
-          <t>1 пара на 1 год</t>
-        </is>
-      </c>
-      <c r="F33" s="13" t="n"/>
-    </row>
-    <row r="34" ht="27" customHeight="1">
+    <row r="34" ht="40.5" customHeight="1">
       <c r="A34" s="13" t="n"/>
       <c r="B34" s="13" t="n"/>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Средства защиты рук</t>
+          <t>Средства защиты ног</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Перчатки для защиты от механических воздействий (истирания, порезов) (Ми, Мп)</t>
+          <t>Обувь специальная для защиты от механических воздействий (ударов в носочной части 200 Дж), с маслобензостойкой противоскользящей подошвой (Мун200)</t>
         </is>
       </c>
       <c r="E34" s="9" t="inlineStr">
         <is>
-          <t>12 пар на 1 год</t>
+          <t>1 пара на 1 год</t>
         </is>
       </c>
       <c r="F34" s="13" t="n"/>
     </row>
-    <row r="35" ht="15" customHeight="1">
+    <row r="35" ht="27" customHeight="1">
       <c r="A35" s="13" t="n"/>
       <c r="B35" s="13" t="n"/>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>Средства защиты головы</t>
+          <t>Средства защиты рук</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>Головной убор для защиты от общих производственных загрязнений</t>
+          <t>Перчатки для защиты от механических воздействий (истирания, порезов) (Ми, Мп)</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
-          <t>1 шт. на 1 год</t>
+          <t>12 пар на 1 год</t>
         </is>
       </c>
       <c r="F35" s="13" t="n"/>
     </row>
-    <row r="36" ht="27" customHeight="1">
+    <row r="36" ht="15" customHeight="1">
       <c r="A36" s="13" t="n"/>
       <c r="B36" s="13" t="n"/>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Средства защиты глаз</t>
+          <t>Средства защиты головы</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Очки защитные от механических воздействий, в том числе с покрытием от запотевания</t>
+          <t>Головной убор для защиты от общих производственных загрязнений</t>
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr">
@@ -1182,19 +1186,19 @@
           <t>1 шт. на 1 год</t>
         </is>
       </c>
-      <c r="F36" s="11" t="n"/>
-    </row>
-    <row r="37" ht="54" customHeight="1">
+      <c r="F36" s="13" t="n"/>
+    </row>
+    <row r="37" ht="27" customHeight="1">
       <c r="A37" s="13" t="n"/>
       <c r="B37" s="13" t="n"/>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>Средства защиты органов дыхания</t>
+          <t>Средства защиты глаз</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>Изолирующая лицевая часть - полумаска многоразовая для использования со сменными фильтрами</t>
+          <t>Очки защитные от механических воздействий, в том числе с покрытием от запотевания</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr">
@@ -1202,206 +1206,206 @@
           <t>1 шт. на 1 год</t>
         </is>
       </c>
-      <c r="F37" s="8" t="inlineStr">
-        <is>
-          <t>Приложение №1 ЕТН, п.4872 (замена фильтрующей полумаски на равноценное СИЗ); Приложение №2 ЕТН, п.7.3.1; п.16 Правил (приказ №766н)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="40.5" customHeight="1">
+      <c r="F37" s="11" t="n"/>
+    </row>
+    <row r="38" ht="54" customHeight="1">
       <c r="A38" s="13" t="n"/>
       <c r="B38" s="13" t="n"/>
-      <c r="C38" s="8" t="n"/>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>Средства защиты органов дыхания</t>
+        </is>
+      </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>Сменные фильтры противоаэрозольные, класс защиты не ниже P1 (при образовании паров СОЖ - противогазоаэрозольные комбинированные)</t>
+          <t>Изолирующая лицевая часть - полумаска многоразовая для использования со сменными фильтрами</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr">
         <is>
-          <t>1 комплект на 5 смен (50 комплектов на 1 год)</t>
-        </is>
-      </c>
-      <c r="F38" s="11" t="n"/>
-    </row>
-    <row r="39" ht="27" customHeight="1">
+          <t>1 шт. на 1 год</t>
+        </is>
+      </c>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>Приложение №1 ЕТН, п.4872 (фильтрующая полумаска заменена на равноценное СИЗ - п.54 Правил, приказ №766н); Приложение №2 ЕТН, п.7.3.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="40.5" customHeight="1">
       <c r="A39" s="13" t="n"/>
       <c r="B39" s="13" t="n"/>
-      <c r="C39" s="8" t="inlineStr">
-        <is>
-          <t>Средства индивидуальной защиты органа слуха</t>
-        </is>
-      </c>
+      <c r="C39" s="8" t="n"/>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>Противошумные вкладыши (беруши) многоразовые</t>
+          <t>Сменные фильтры противоаэрозольные, класс защиты не ниже P1 (при образовании паров СОЖ - противогазоаэрозольные комбинированные)</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
         <is>
-          <t>12 пар на 1 год (1 пара на 1 месяц)</t>
-        </is>
-      </c>
-      <c r="F39" s="8" t="inlineStr">
-        <is>
-          <t>Приложение №2 ЕТН, п.10.1.1 (опасность идентифицирована по результатам ОПР)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="15" customHeight="1">
+          <t>1 комплект на 5 смен (50 комплектов на 1 год)</t>
+        </is>
+      </c>
+      <c r="F39" s="11" t="n"/>
+    </row>
+    <row r="40" ht="27" customHeight="1">
       <c r="A40" s="13" t="n"/>
       <c r="B40" s="13" t="n"/>
-      <c r="C40" s="8" t="n"/>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>Средства индивидуальной защиты органа слуха</t>
+        </is>
+      </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>или Противошумные наушники</t>
+          <t>Противошумные вкладыши (беруши) многоразовые</t>
         </is>
       </c>
       <c r="E40" s="9" t="inlineStr">
         <is>
-          <t>1 шт. на 1 год</t>
-        </is>
-      </c>
-      <c r="F40" s="11" t="n"/>
+          <t>12 пар на 1 год (1 пара на 1 месяц)</t>
+        </is>
+      </c>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t>Приложение №2 ЕТН, п.10.1.1 (опасность идентифицирована по результатам ОПР)</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" s="13" t="n"/>
       <c r="B41" s="13" t="n"/>
-      <c r="C41" s="12" t="inlineStr">
-        <is>
-          <t>При обработке деталей с образованием сливной стружки, при работе на станке без защитного экрана:</t>
-        </is>
-      </c>
-      <c r="D41" s="17" t="n"/>
-      <c r="E41" s="17" t="n"/>
-      <c r="F41" s="18" t="n"/>
-    </row>
-    <row r="42" ht="40.5" customHeight="1">
+      <c r="C41" s="8" t="n"/>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>или Противошумные наушники</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="inlineStr">
+        <is>
+          <t>1 шт. на 1 год</t>
+        </is>
+      </c>
+      <c r="F41" s="11" t="n"/>
+    </row>
+    <row r="42" ht="15" customHeight="1">
       <c r="A42" s="13" t="n"/>
       <c r="B42" s="13" t="n"/>
-      <c r="C42" s="8" t="inlineStr">
-        <is>
-          <t>Средства индивидуальной защиты глаз и лица от механических воздействий</t>
-        </is>
-      </c>
-      <c r="D42" s="8" t="inlineStr">
-        <is>
-          <t>Щиток защитный лицевой от механических воздействий (ударов твердых частиц)</t>
-        </is>
-      </c>
-      <c r="E42" s="9" t="inlineStr">
-        <is>
-          <t>1 шт. на 1 год</t>
-        </is>
-      </c>
-      <c r="F42" s="8" t="inlineStr">
-        <is>
-          <t>Приложение №2 ЕТН, п.1.21.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="15" customHeight="1">
+      <c r="C42" s="12" t="inlineStr">
+        <is>
+          <t>При обработке деталей с образованием сливной стружки, при работе на станке без защитного экрана:</t>
+        </is>
+      </c>
+      <c r="D42" s="17" t="n"/>
+      <c r="E42" s="17" t="n"/>
+      <c r="F42" s="18" t="n"/>
+    </row>
+    <row r="43" ht="40.5" customHeight="1">
       <c r="A43" s="13" t="n"/>
       <c r="B43" s="13" t="n"/>
-      <c r="C43" s="12" t="inlineStr">
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>Средства индивидуальной защиты глаз и лица от механических воздействий</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>Щиток защитный лицевой от механических воздействий (ударов твердых частиц)</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="inlineStr">
+        <is>
+          <t>1 шт. на 1 год</t>
+        </is>
+      </c>
+      <c r="F43" s="8" t="inlineStr">
+        <is>
+          <t>Приложение №2 ЕТН, п.1.21.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="15" customHeight="1">
+      <c r="A44" s="13" t="n"/>
+      <c r="B44" s="13" t="n"/>
+      <c r="C44" s="12" t="inlineStr">
         <is>
           <t>При допуске к управлению подъёмными сооружениями (кран-балка, таль) с пола:</t>
         </is>
       </c>
-      <c r="D43" s="17" t="n"/>
-      <c r="E43" s="17" t="n"/>
-      <c r="F43" s="18" t="n"/>
-    </row>
-    <row r="44" ht="27" customHeight="1">
-      <c r="A44" s="11" t="n"/>
-      <c r="B44" s="11" t="n"/>
-      <c r="C44" s="8" t="inlineStr">
+      <c r="D44" s="17" t="n"/>
+      <c r="E44" s="17" t="n"/>
+      <c r="F44" s="18" t="n"/>
+    </row>
+    <row r="45" ht="27" customHeight="1">
+      <c r="A45" s="11" t="n"/>
+      <c r="B45" s="11" t="n"/>
+      <c r="C45" s="8" t="inlineStr">
         <is>
           <t>Средства индивидуальной защиты головы от механических воздействий</t>
         </is>
       </c>
-      <c r="D44" s="8" t="inlineStr">
+      <c r="D45" s="8" t="inlineStr">
         <is>
           <t>Каска защитная</t>
         </is>
       </c>
-      <c r="E44" s="9" t="inlineStr">
+      <c r="E45" s="9" t="inlineStr">
         <is>
           <t>1 шт. на 2 года</t>
         </is>
       </c>
-      <c r="F44" s="8" t="inlineStr">
+      <c r="F45" s="8" t="inlineStr">
         <is>
           <t>Приложение №2 ЕТН, п.1.3.1</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="15" customHeight="1">
-      <c r="A45" s="6" t="n">
+    <row r="46" ht="15" customHeight="1">
+      <c r="A46" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B45" s="7" t="inlineStr">
+      <c r="B46" s="7" t="inlineStr">
         <is>
           <t>Слесарь механосборочных работ</t>
         </is>
       </c>
-      <c r="C45" s="8" t="inlineStr">
+      <c r="C46" s="8" t="inlineStr">
         <is>
           <t>Одежда специальная защитная</t>
         </is>
       </c>
-      <c r="D45" s="8" t="inlineStr">
+      <c r="D46" s="8" t="inlineStr">
         <is>
           <t>Костюм для защиты от механических воздействий (истирания) (Ми)</t>
         </is>
       </c>
-      <c r="E45" s="9" t="inlineStr">
+      <c r="E46" s="9" t="inlineStr">
         <is>
           <t>1 шт. на 1 год</t>
         </is>
       </c>
-      <c r="F45" s="8" t="inlineStr">
+      <c r="F46" s="8" t="inlineStr">
         <is>
           <t>Приложение №1 ЕТН, п.4516</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="40.5" customHeight="1">
-      <c r="A46" s="13" t="n"/>
-      <c r="B46" s="13" t="n"/>
-      <c r="C46" s="8" t="inlineStr">
-        <is>
-          <t>Средства защиты ног</t>
-        </is>
-      </c>
-      <c r="D46" s="8" t="inlineStr">
-        <is>
-          <t>Обувь специальная для защиты от механических воздействий (ударов в носочной части 200 Дж), с маслобензостойкой противоскользящей подошвой (Мун200)</t>
-        </is>
-      </c>
-      <c r="E46" s="9" t="inlineStr">
-        <is>
-          <t>1 пара на 1 год</t>
-        </is>
-      </c>
-      <c r="F46" s="13" t="n"/>
-    </row>
-    <row r="47" ht="15" customHeight="1">
+    <row r="47" ht="40.5" customHeight="1">
       <c r="A47" s="13" t="n"/>
       <c r="B47" s="13" t="n"/>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>Средства защиты рук</t>
+          <t>Средства защиты ног</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>Перчатки для защиты от механических воздействий (истирания) (Ми)</t>
+          <t>Обувь специальная для защиты от механических воздействий (ударов в носочной части 200 Дж), с маслобензостойкой противоскользящей подошвой (Мун200)</t>
         </is>
       </c>
       <c r="E47" s="9" t="inlineStr">
         <is>
-          <t>12 пар на 1 год</t>
+          <t>1 пара на 1 год</t>
         </is>
       </c>
       <c r="F47" s="13" t="n"/>
@@ -1411,17 +1415,17 @@
       <c r="B48" s="13" t="n"/>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Средства защиты головы</t>
+          <t>Средства защиты рук</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Головной убор для защиты от общих производственных загрязнений</t>
+          <t>Перчатки для защиты от механических воздействий (истирания) (Ми)</t>
         </is>
       </c>
       <c r="E48" s="9" t="inlineStr">
         <is>
-          <t>1 шт. на 1 год</t>
+          <t>12 пар на 1 год</t>
         </is>
       </c>
       <c r="F48" s="13" t="n"/>
@@ -1429,268 +1433,276 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" s="13" t="n"/>
       <c r="B49" s="13" t="n"/>
-      <c r="C49" s="8" t="n"/>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>Средства защиты головы</t>
+        </is>
+      </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>Каска защитная от механических воздействий</t>
+          <t>Головной убор для защиты от общих производственных загрязнений</t>
         </is>
       </c>
       <c r="E49" s="9" t="inlineStr">
         <is>
-          <t>1 шт. на 2 года</t>
+          <t>1 шт. на 1 год</t>
         </is>
       </c>
       <c r="F49" s="13" t="n"/>
     </row>
-    <row r="50" ht="27" customHeight="1">
+    <row r="50" ht="15" customHeight="1">
       <c r="A50" s="13" t="n"/>
       <c r="B50" s="13" t="n"/>
-      <c r="C50" s="8" t="inlineStr">
-        <is>
-          <t>Средства защиты глаз</t>
-        </is>
-      </c>
+      <c r="C50" s="8" t="n"/>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>Очки защитные от механических воздействий, в том числе с покрытием от запотевания</t>
+          <t>Каска защитная от механических воздействий</t>
         </is>
       </c>
       <c r="E50" s="9" t="inlineStr">
         <is>
-          <t>1 шт. на 1 год</t>
-        </is>
-      </c>
-      <c r="F50" s="11" t="n"/>
+          <t>1 шт. на 2 года</t>
+        </is>
+      </c>
+      <c r="F50" s="13" t="n"/>
     </row>
     <row r="51" ht="27" customHeight="1">
       <c r="A51" s="13" t="n"/>
       <c r="B51" s="13" t="n"/>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>Средства индивидуальной защиты органа слуха</t>
+          <t>Средства защиты глаз</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>Противошумные вкладыши (беруши) многоразовые</t>
+          <t>Очки защитные от механических воздействий, в том числе с покрытием от запотевания</t>
         </is>
       </c>
       <c r="E51" s="9" t="inlineStr">
         <is>
-          <t>12 пар на 1 год (1 пара на 1 месяц)</t>
-        </is>
-      </c>
-      <c r="F51" s="8" t="inlineStr">
-        <is>
-          <t>Приложение №2 ЕТН, п.10.1.1 (опасность идентифицирована по результатам ОПР)</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="15" customHeight="1">
+          <t>1 шт. на 1 год</t>
+        </is>
+      </c>
+      <c r="F51" s="11" t="n"/>
+    </row>
+    <row r="52" ht="27" customHeight="1">
       <c r="A52" s="13" t="n"/>
       <c r="B52" s="13" t="n"/>
-      <c r="C52" s="8" t="n"/>
+      <c r="C52" s="8" t="inlineStr">
+        <is>
+          <t>Средства индивидуальной защиты органа слуха</t>
+        </is>
+      </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>или Противошумные наушники</t>
+          <t>Противошумные вкладыши (беруши) многоразовые</t>
         </is>
       </c>
       <c r="E52" s="9" t="inlineStr">
         <is>
-          <t>1 шт. на 1 год</t>
-        </is>
-      </c>
-      <c r="F52" s="11" t="n"/>
+          <t>12 пар на 1 год (1 пара на 1 месяц)</t>
+        </is>
+      </c>
+      <c r="F52" s="8" t="inlineStr">
+        <is>
+          <t>Приложение №2 ЕТН, п.10.1.1 (опасность идентифицирована по результатам ОПР)</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="15" customHeight="1">
       <c r="A53" s="13" t="n"/>
       <c r="B53" s="13" t="n"/>
-      <c r="C53" s="12" t="inlineStr">
-        <is>
-          <t>При работе ручным шлифовальным (абразивным) инструментом, зачистке заусенцев:</t>
-        </is>
-      </c>
-      <c r="D53" s="17" t="n"/>
-      <c r="E53" s="17" t="n"/>
-      <c r="F53" s="18" t="n"/>
-    </row>
-    <row r="54" ht="40.5" customHeight="1">
+      <c r="C53" s="8" t="n"/>
+      <c r="D53" s="8" t="inlineStr">
+        <is>
+          <t>или Противошумные наушники</t>
+        </is>
+      </c>
+      <c r="E53" s="9" t="inlineStr">
+        <is>
+          <t>1 шт. на 1 год</t>
+        </is>
+      </c>
+      <c r="F53" s="11" t="n"/>
+    </row>
+    <row r="54" ht="15" customHeight="1">
       <c r="A54" s="13" t="n"/>
       <c r="B54" s="13" t="n"/>
-      <c r="C54" s="8" t="inlineStr">
-        <is>
-          <t>Средства индивидуальной защиты глаз и лица от механических воздействий</t>
-        </is>
-      </c>
-      <c r="D54" s="8" t="inlineStr">
-        <is>
-          <t>Щиток защитный лицевой от механических воздействий (ударов твердых частиц)</t>
-        </is>
-      </c>
-      <c r="E54" s="9" t="inlineStr">
-        <is>
-          <t>1 шт. на 1 год</t>
-        </is>
-      </c>
-      <c r="F54" s="8" t="inlineStr">
-        <is>
-          <t>Приложение №2 ЕТН, п.1.24.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="54" customHeight="1">
+      <c r="C54" s="12" t="inlineStr">
+        <is>
+          <t>При работе ручным шлифовальным (абразивным) инструментом, зачистке заусенцев:</t>
+        </is>
+      </c>
+      <c r="D54" s="17" t="n"/>
+      <c r="E54" s="17" t="n"/>
+      <c r="F54" s="18" t="n"/>
+    </row>
+    <row r="55" ht="40.5" customHeight="1">
       <c r="A55" s="13" t="n"/>
       <c r="B55" s="13" t="n"/>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>Средства индивидуальной защиты органов дыхания фильтрующего типа противоаэрозольные</t>
+          <t>Средства индивидуальной защиты глаз и лица от механических воздействий</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>Противоаэрозольные средства индивидуальной защиты органов дыхания с фильтрующей лицевой частью - фильтрующие полумаски одноразовые, класс защиты не ниже FFP2</t>
+          <t>Щиток защитный лицевой от механических воздействий (ударов твердых частиц)</t>
         </is>
       </c>
       <c r="E55" s="9" t="inlineStr">
         <is>
-          <t>1 шт. на смену выполнения указанных работ, не более 247 шт. на 1 год</t>
+          <t>1 шт. на 1 год</t>
         </is>
       </c>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>Приложение №2 ЕТН, п.7.1.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="15" customHeight="1">
+          <t>Приложение №2 ЕТН, п.1.24.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="54" customHeight="1">
       <c r="A56" s="13" t="n"/>
       <c r="B56" s="13" t="n"/>
-      <c r="C56" s="12" t="inlineStr">
-        <is>
-          <t>При выполнении работ в неотапливаемых помещениях, на открытом воздухе в холодный период года:</t>
-        </is>
-      </c>
-      <c r="D56" s="17" t="n"/>
-      <c r="E56" s="17" t="n"/>
-      <c r="F56" s="18" t="n"/>
-    </row>
-    <row r="57" ht="27" customHeight="1">
-      <c r="A57" s="11" t="n"/>
-      <c r="B57" s="11" t="n"/>
-      <c r="C57" s="8" t="inlineStr">
+      <c r="C56" s="8" t="inlineStr">
+        <is>
+          <t>Средства индивидуальной защиты органов дыхания фильтрующего типа противоаэрозольные</t>
+        </is>
+      </c>
+      <c r="D56" s="8" t="inlineStr">
+        <is>
+          <t>Противоаэрозольные средства индивидуальной защиты органов дыхания с фильтрующей лицевой частью - фильтрующие полумаски одноразовые, класс защиты не ниже FFP2</t>
+        </is>
+      </c>
+      <c r="E56" s="9" t="inlineStr">
+        <is>
+          <t>1 шт. на смену выполнения указанных работ, не более 247 шт. на 1 год</t>
+        </is>
+      </c>
+      <c r="F56" s="8" t="inlineStr">
+        <is>
+          <t>Приложение №2 ЕТН, п.7.1.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="15" customHeight="1">
+      <c r="A57" s="13" t="n"/>
+      <c r="B57" s="13" t="n"/>
+      <c r="C57" s="12" t="inlineStr">
+        <is>
+          <t>При кратковременной работе в неотапливаемых помещениях, на открытом воздухе в холодный период года (погрузка, выгрузка, перемещение между зданиями):</t>
+        </is>
+      </c>
+      <c r="D57" s="17" t="n"/>
+      <c r="E57" s="17" t="n"/>
+      <c r="F57" s="18" t="n"/>
+    </row>
+    <row r="58" ht="40.5" customHeight="1">
+      <c r="A58" s="11" t="n"/>
+      <c r="B58" s="11" t="n"/>
+      <c r="C58" s="8" t="inlineStr">
         <is>
           <t>Одежда специальная для защиты от пониженных температур</t>
         </is>
       </c>
-      <c r="D57" s="8" t="inlineStr">
-        <is>
-          <t>Куртка утепленная для защиты от пониженных температур (класс защиты Тн по климатическому поясу места нахождения предприятия)</t>
-        </is>
-      </c>
-      <c r="E57" s="9" t="inlineStr">
+      <c r="D58" s="8" t="inlineStr">
+        <is>
+          <t>Куртка утепленная для защиты от пониженных температур, 1 класс защиты (II климатический пояс); выдается на холодный период года с последующей сдачей на хранение</t>
+        </is>
+      </c>
+      <c r="E58" s="9" t="inlineStr">
         <is>
           <t>1 шт. на 2 года</t>
         </is>
       </c>
-      <c r="F57" s="8" t="inlineStr">
-        <is>
-          <t>Приложение №2 ЕТН, п.4.7.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="15" customHeight="1"/>
-    <row r="59" ht="15" customHeight="1">
-      <c r="B59" s="14" t="inlineStr">
+      <c r="F58" s="8" t="inlineStr">
+        <is>
+          <t>Приложение №2 ЕТН, п.4.7.1; пп.48, 50, Приложение №4 Правил (приказ №766н)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="15" customHeight="1"/>
+    <row r="60" ht="15" customHeight="1">
+      <c r="B60" s="14" t="inlineStr">
         <is>
           <t>Примечания:</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="30" customHeight="1">
-      <c r="B60" s="15" t="inlineStr">
-        <is>
-          <t>1. Выдаются СИЗ, имеющие действующий сертификат или декларацию соответствия ТР ТС 019/2011 (п.7 Правил, приказ №766н), с защитными свойствами, указанными в графе 4.</t>
         </is>
       </c>
     </row>
     <row r="61" ht="30" customHeight="1">
       <c r="B61" s="15" t="inlineStr">
         <is>
-          <t>2. СИЗ органа слуха установлены по результатам ОПР (опасность «повышенный уровень шума», п.10.1 Приложения №2 ЕТН). СОУТ по фактору «шум» не проводилась: после проведения СОУТ (измерений) эффективность СИЗ (SNR) подтверждается по фактическому уровню шума, нормы актуализируются (п.19 Правил).</t>
+          <t>1. Выдаются СИЗ, имеющие действующий сертификат или декларацию соответствия ТР ТС 019/2011 (п.7 Правил, приказ №766н), с защитными свойствами, указанными в графе 4.</t>
         </is>
       </c>
     </row>
     <row r="62" ht="30" customHeight="1">
       <c r="B62" s="15" t="inlineStr">
         <is>
-          <t>3. Работа в перчатках на станках с вращающимися частями (шпиндель, патрон, заготовка) запрещена (Правила по охране труда при обработке металлов, приказ Минтруда России №887н). Перчатки применяются при установке/снятии заготовок, уборке стружки, слесарных операциях.</t>
+          <t>2. СИЗ органа слуха установлены по результатам ОПР (опасность «повышенный уровень шума», п.10.1 Приложения №2 ЕТН). СОУТ по фактору «шум» не проводилась: после проведения СОУТ (измерений) эффективность СИЗ (SNR) подтверждается по фактическому уровню шума, нормы актуализируются (п.19 Правил).</t>
         </is>
       </c>
     </row>
     <row r="63" ht="30" customHeight="1">
       <c r="B63" s="15" t="inlineStr">
         <is>
-          <t>4. СИЗ по строкам «При …» выдаются работникам, фактически выполняющим указанные работы (перечень утверждается распоряжением по участку).</t>
+          <t>3. Работа в перчатках на станках с вращающимися частями (шпиндель, патрон, заготовка) запрещена (раздел LXXVI Правил по охране труда при обработке металлов, приказ Минтруда России №887н). Перчатки применяются при установке/снятии заготовок, уборке стружки, слесарных операциях.</t>
         </is>
       </c>
     </row>
     <row r="64" ht="30" customHeight="1">
       <c r="B64" s="15" t="inlineStr">
         <is>
-          <t>5. Количество одноразовых СИЗ органов дыхания и сменных фильтров рассчитано на 247 рабочих смен (производственный календарь 2026 г., пятидневная рабочая неделя).</t>
+          <t>4. СИЗ по строкам «При …» выдаются работникам, фактически выполняющим указанные работы (перечень утверждается распоряжением по участку).</t>
         </is>
       </c>
     </row>
     <row r="65" ht="30" customHeight="1">
       <c r="B65" s="15" t="inlineStr">
         <is>
+          <t>5. Количество одноразовых СИЗ органов дыхания и сменных фильтров рассчитано на 247 рабочих смен (производственный календарь 2026 г., пятидневная рабочая неделя). СИЗ, выдаваемые 1 раз в месяц и чаще, выдаются с учетом времени, фактически отработанного на рабочем месте, без учета отпусков (п.58 Правил).</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="30" customHeight="1">
+      <c r="B66" s="15" t="inlineStr">
+        <is>
           <t>6. Нормы подлежат сверке с результатами СОУТ и ОПР и актуализации при их изменении (п.14, п.19 Правил, приказ №766н).</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="15" customHeight="1"/>
-    <row r="67" ht="15" customHeight="1">
-      <c r="B67" s="4" t="inlineStr">
+    <row r="67" ht="15" customHeight="1"/>
+    <row r="68" ht="15" customHeight="1">
+      <c r="B68" s="4" t="inlineStr">
         <is>
           <t>Разработал:</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="32" customHeight="1">
-      <c r="B68" s="16" t="inlineStr">
+    <row r="69" ht="32" customHeight="1">
+      <c r="B69" s="16" t="inlineStr">
         <is>
           <t>Начальник отдела охраны труда и промышленной безопасности</t>
         </is>
       </c>
-      <c r="D68" s="16" t="inlineStr">
+      <c r="D69" s="16" t="inlineStr">
         <is>
           <t>________________ / ____________</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="15" customHeight="1">
-      <c r="B69" s="4" t="inlineStr">
+    <row r="70" ht="15" customHeight="1">
+      <c r="B70" s="4" t="inlineStr">
         <is>
           <t>Согласовано:</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="32" customHeight="1">
-      <c r="B70" s="16" t="inlineStr">
-        <is>
-          <t>Директор по производству</t>
-        </is>
-      </c>
-      <c r="D70" s="16" t="inlineStr">
-        <is>
-          <t>________________ / ____________</t>
         </is>
       </c>
     </row>
     <row r="71" ht="32" customHeight="1">
       <c r="B71" s="16" t="inlineStr">
         <is>
-          <t>Начальник участка</t>
+          <t>Директор по производству</t>
         </is>
       </c>
       <c r="D71" s="16" t="inlineStr">
@@ -1702,7 +1714,7 @@
     <row r="72" ht="32" customHeight="1">
       <c r="B72" s="16" t="inlineStr">
         <is>
-          <t>Мастер участка</t>
+          <t>Начальник участка</t>
         </is>
       </c>
       <c r="D72" s="16" t="inlineStr">
@@ -1714,10 +1726,22 @@
     <row r="73" ht="32" customHeight="1">
       <c r="B73" s="16" t="inlineStr">
         <is>
+          <t>Мастер участка</t>
+        </is>
+      </c>
+      <c r="D73" s="16" t="inlineStr">
+        <is>
+          <t>________________ / ____________</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="32" customHeight="1">
+      <c r="B74" s="16" t="inlineStr">
+        <is>
           <t>Представитель выборного органа первичной профсоюзной организации (при наличии)</t>
         </is>
       </c>
-      <c r="D73" s="16" t="inlineStr">
+      <c r="D74" s="16" t="inlineStr">
         <is>
           <t>________________ / ____________</t>
         </is>
@@ -1726,47 +1750,47 @@
   </sheetData>
   <mergeCells count="42">
     <mergeCell ref="D2:F2"/>
-    <mergeCell ref="F32:F36"/>
+    <mergeCell ref="F40:F41"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="B62:F62"/>
     <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B59:F59"/>
-    <mergeCell ref="A45:A57"/>
-    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="B13:B21"/>
+    <mergeCell ref="B66:F66"/>
+    <mergeCell ref="C57:F57"/>
     <mergeCell ref="B71:C71"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="C53:F53"/>
-    <mergeCell ref="F45:F50"/>
-    <mergeCell ref="A21:A31"/>
-    <mergeCell ref="F21:F24"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="F51:F52"/>
+    <mergeCell ref="F18:F19"/>
     <mergeCell ref="D4:F4"/>
-    <mergeCell ref="F17:F18"/>
     <mergeCell ref="B60:F60"/>
-    <mergeCell ref="C30:F30"/>
     <mergeCell ref="D3:F3"/>
+    <mergeCell ref="A46:A58"/>
+    <mergeCell ref="A33:A45"/>
     <mergeCell ref="B61:F61"/>
+    <mergeCell ref="C42:F42"/>
     <mergeCell ref="B73:C73"/>
-    <mergeCell ref="A32:A44"/>
+    <mergeCell ref="A13:A21"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="A22:A32"/>
+    <mergeCell ref="F22:F25"/>
+    <mergeCell ref="F27:F28"/>
     <mergeCell ref="D5:F5"/>
-    <mergeCell ref="F37:F38"/>
-    <mergeCell ref="F39:F40"/>
-    <mergeCell ref="C41:F41"/>
+    <mergeCell ref="F38:F39"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="F52:F53"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="B33:B45"/>
+    <mergeCell ref="C54:F54"/>
+    <mergeCell ref="F46:F51"/>
     <mergeCell ref="D1:F1"/>
-    <mergeCell ref="B13:B20"/>
-    <mergeCell ref="B45:B57"/>
+    <mergeCell ref="C44:F44"/>
     <mergeCell ref="B65:F65"/>
+    <mergeCell ref="B74:C74"/>
     <mergeCell ref="C9:F9"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="C56:F56"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="B22:B32"/>
     <mergeCell ref="B64:F64"/>
-    <mergeCell ref="C43:F43"/>
+    <mergeCell ref="F33:F37"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B21:B31"/>
-    <mergeCell ref="B32:B44"/>
-    <mergeCell ref="A13:A20"/>
+    <mergeCell ref="B46:B58"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -1779,7 +1803,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.3" customWidth="1" min="1" max="1"/>
@@ -1848,7 +1872,7 @@
       </c>
     </row>
     <row r="10" ht="15" customHeight="1"/>
-    <row r="11" ht="64" customHeight="1">
+    <row r="11" ht="67.5" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
           <t>№ п/п</t>
@@ -1856,7 +1880,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Должность работника</t>
+          <t>Наименование профессии (должности)</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -1871,12 +1895,12 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Нормы выдачи на год (период), единицы измерения (штуки, пары, комплекты)</t>
+          <t>Нормы выдачи с указанием периодичности выдачи, количества на период, единицы измерения (штуки, пары, комплекты, г, мл.)</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Основание выдачи СИЗ (пункты Единых типовых норм (ЕТН), правил по охране труда и иных документов)</t>
+          <t>Основание выдачи СИЗ (пункты Единых типовых норм, правил по охране труда и иных документов)</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1924,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" ht="40.5" customHeight="1">
+    <row r="13" ht="54" customHeight="1">
       <c r="A13" s="6" t="n">
         <v>1</v>
       </c>
@@ -1916,7 +1940,7 @@
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>Костюм для защиты от общих производственных загрязнений (З)</t>
+          <t>Костюм для защиты от общих производственных загрязнений и механических воздействий (истирания) (З, Ми)</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
@@ -1926,7 +1950,7 @@
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>Приложение №2 ЕТН, п.2.1.1; п.18 Правил обеспечения работников СИЗ (приказ Минтруда №766н)</t>
+          <t>Приложение №2 ЕТН, п.2.1.1; Приложение №1 ЕТН, п.4562 (по виду контролируемых работ); п.18 Правил обеспечения работников СИЗ (приказ Минтруда №766н)</t>
         </is>
       </c>
     </row>
@@ -1959,56 +1983,60 @@
       <c r="B15" s="13" t="n"/>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Средства индивидуальной защиты глаз и лица от механических воздействий</t>
+          <t>Средства защиты рук</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>Очки защитные открытые от механических воздействий, класс оптики 1, прочность не ниже F, с покрытием от запотевания</t>
+          <t>Перчатки для защиты от механических воздействий (истирания) (Ми)</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>1 шт. на 1 год</t>
+          <t>12 пар на 1 год</t>
         </is>
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>Приложение №2 ЕТН, п.1.24.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="27" customHeight="1">
+          <t>Приложение №1 ЕТН (по виду контролируемых работ); п.18 Правил обеспечения работников СИЗ (приказ Минтруда №766н)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
       <c r="A16" s="13" t="n"/>
       <c r="B16" s="13" t="n"/>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Средства индивидуальной защиты органа слуха</t>
+          <t>Средства защиты головы</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Противошумные вкладыши (беруши) многоразовые</t>
+          <t>Головной убор для защиты от общих производственных загрязнений</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>12 пар на 1 год (1 пара на 1 месяц)</t>
+          <t>1 шт. на 1 год</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>Приложение №2 ЕТН, п.10.1.1 (опасность идентифицирована по результатам ОПР)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
+          <t>Приложение №2 ЕТН, п.2.1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="40.5" customHeight="1">
       <c r="A17" s="13" t="n"/>
       <c r="B17" s="13" t="n"/>
-      <c r="C17" s="8" t="n"/>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Средства индивидуальной защиты глаз и лица от механических воздействий</t>
+        </is>
+      </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>или Противошумные наушники</t>
+          <t>Очки защитные открытые от механических воздействий, класс оптики 1, прочность не ниже F, с покрытием от запотевания</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
@@ -2016,185 +2044,189 @@
           <t>1 шт. на 1 год</t>
         </is>
       </c>
-      <c r="F17" s="11" t="n"/>
-    </row>
-    <row r="18" ht="15" customHeight="1">
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>Приложение №2 ЕТН, п.1.24.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="27" customHeight="1">
       <c r="A18" s="13" t="n"/>
       <c r="B18" s="13" t="n"/>
-      <c r="C18" s="12" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Средства индивидуальной защиты органа слуха</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>Противошумные вкладыши (беруши) многоразовые</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>12 пар на 1 год (1 пара на 1 месяц)</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>Приложение №2 ЕТН, п.10.1.1 (опасность идентифицирована по результатам ОПР)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" s="13" t="n"/>
+      <c r="B19" s="13" t="n"/>
+      <c r="C19" s="8" t="n"/>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>или Противошумные наушники</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>1 шт. на 1 год</t>
+        </is>
+      </c>
+      <c r="F19" s="11" t="n"/>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" s="13" t="n"/>
+      <c r="B20" s="13" t="n"/>
+      <c r="C20" s="12" t="inlineStr">
         <is>
           <t>При допуске к управлению подъёмными сооружениями (кран-балка, таль) с пола:</t>
         </is>
       </c>
-      <c r="D18" s="17" t="n"/>
-      <c r="E18" s="17" t="n"/>
-      <c r="F18" s="18" t="n"/>
-    </row>
-    <row r="19" ht="27" customHeight="1">
-      <c r="A19" s="11" t="n"/>
-      <c r="B19" s="11" t="n"/>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="D20" s="17" t="n"/>
+      <c r="E20" s="17" t="n"/>
+      <c r="F20" s="18" t="n"/>
+    </row>
+    <row r="21" ht="27" customHeight="1">
+      <c r="A21" s="11" t="n"/>
+      <c r="B21" s="11" t="n"/>
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>Средства индивидуальной защиты головы от механических воздействий</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t>Каска защитная</t>
         </is>
       </c>
-      <c r="E19" s="9" t="inlineStr">
+      <c r="E21" s="9" t="inlineStr">
         <is>
           <t>1 шт. на 2 года</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="F21" s="8" t="inlineStr">
         <is>
           <t>Приложение №2 ЕТН, п.1.3.1</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="40.5" customHeight="1">
-      <c r="A20" s="6" t="n">
+    <row r="22" ht="40.5" customHeight="1">
+      <c r="A22" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>Мастер участка</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>Одежда специальная защитная</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>Костюм для защиты от механических воздействий (истирания) (Ми)</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="E22" s="9" t="inlineStr">
         <is>
           <t>1 шт. на 1 год</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="F22" s="8" t="inlineStr">
         <is>
           <t>Приложение №1 ЕТН, п.4562 (по виду контролируемых работ); п.18 Правил обеспечения работников СИЗ (приказ Минтруда №766н)</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="40.5" customHeight="1">
-      <c r="A21" s="13" t="n"/>
-      <c r="B21" s="13" t="n"/>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>Средства защиты ног</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>Обувь специальная для защиты от механических воздействий (ударов в носочной части 200 Дж), с маслобензостойкой противоскользящей подошвой (Мун200)</t>
-        </is>
-      </c>
-      <c r="E21" s="9" t="inlineStr">
-        <is>
-          <t>1 пара на 1 год</t>
-        </is>
-      </c>
-      <c r="F21" s="13" t="n"/>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="13" t="n"/>
-      <c r="B22" s="13" t="n"/>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>Средства защиты рук</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>Перчатки для защиты от механических воздействий (истирания) (Ми)</t>
-        </is>
-      </c>
-      <c r="E22" s="9" t="inlineStr">
-        <is>
-          <t>12 пар на 1 год</t>
-        </is>
-      </c>
-      <c r="F22" s="13" t="n"/>
-    </row>
-    <row r="23" ht="15" customHeight="1">
+    <row r="23" ht="40.5" customHeight="1">
       <c r="A23" s="13" t="n"/>
       <c r="B23" s="13" t="n"/>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Средства защиты головы</t>
+          <t>Средства защиты ног</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>Головной убор для защиты от общих производственных загрязнений</t>
+          <t>Обувь специальная для защиты от механических воздействий (ударов в носочной части 200 Дж), с маслобензостойкой противоскользящей подошвой (Мун200)</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>1 шт. на 1 год</t>
+          <t>1 пара на 1 год</t>
         </is>
       </c>
       <c r="F23" s="13" t="n"/>
     </row>
-    <row r="24" ht="27" customHeight="1">
+    <row r="24" ht="15" customHeight="1">
       <c r="A24" s="13" t="n"/>
       <c r="B24" s="13" t="n"/>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Средства защиты глаз</t>
+          <t>Средства защиты рук</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Очки защитные от механических воздействий, в том числе с покрытием от запотевания</t>
+          <t>Перчатки для защиты от механических воздействий (истирания) (Ми)</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>1 шт. на 1 год</t>
-        </is>
-      </c>
-      <c r="F24" s="11" t="n"/>
-    </row>
-    <row r="25" ht="27" customHeight="1">
+          <t>12 пар на 1 год</t>
+        </is>
+      </c>
+      <c r="F24" s="13" t="n"/>
+    </row>
+    <row r="25" ht="15" customHeight="1">
       <c r="A25" s="13" t="n"/>
       <c r="B25" s="13" t="n"/>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>Средства индивидуальной защиты органа слуха</t>
+          <t>Средства защиты головы</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>Противошумные вкладыши (беруши) многоразовые</t>
+          <t>Головной убор для защиты от общих производственных загрязнений</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>12 пар на 1 год (1 пара на 1 месяц)</t>
-        </is>
-      </c>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>Приложение №2 ЕТН, п.10.1.1 (опасность идентифицирована по результатам ОПР)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
+          <t>1 шт. на 1 год</t>
+        </is>
+      </c>
+      <c r="F25" s="13" t="n"/>
+    </row>
+    <row r="26" ht="27" customHeight="1">
       <c r="A26" s="13" t="n"/>
       <c r="B26" s="13" t="n"/>
-      <c r="C26" s="8" t="n"/>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>Средства защиты глаз</t>
+        </is>
+      </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>или Противошумные наушники</t>
+          <t>Очки защитные от механических воздействий, в том числе с покрытием от запотевания</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
@@ -2204,183 +2236,183 @@
       </c>
       <c r="F26" s="11" t="n"/>
     </row>
-    <row r="27" ht="15" customHeight="1">
+    <row r="27" ht="27" customHeight="1">
       <c r="A27" s="13" t="n"/>
       <c r="B27" s="13" t="n"/>
-      <c r="C27" s="12" t="inlineStr">
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>Средства индивидуальной защиты органа слуха</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>Противошумные вкладыши (беруши) многоразовые</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>12 пар на 1 год (1 пара на 1 месяц)</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>Приложение №2 ЕТН, п.10.1.1 (опасность идентифицирована по результатам ОПР)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" s="13" t="n"/>
+      <c r="B28" s="13" t="n"/>
+      <c r="C28" s="8" t="n"/>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>или Противошумные наушники</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>1 шт. на 1 год</t>
+        </is>
+      </c>
+      <c r="F28" s="11" t="n"/>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" s="13" t="n"/>
+      <c r="B29" s="13" t="n"/>
+      <c r="C29" s="12" t="inlineStr">
         <is>
           <t>При допуске к управлению подъёмными сооружениями (кран-балка, таль) с пола:</t>
         </is>
       </c>
-      <c r="D27" s="17" t="n"/>
-      <c r="E27" s="17" t="n"/>
-      <c r="F27" s="18" t="n"/>
-    </row>
-    <row r="28" ht="27" customHeight="1">
-      <c r="A28" s="11" t="n"/>
-      <c r="B28" s="11" t="n"/>
-      <c r="C28" s="8" t="inlineStr">
+      <c r="D29" s="17" t="n"/>
+      <c r="E29" s="17" t="n"/>
+      <c r="F29" s="18" t="n"/>
+    </row>
+    <row r="30" ht="27" customHeight="1">
+      <c r="A30" s="11" t="n"/>
+      <c r="B30" s="11" t="n"/>
+      <c r="C30" s="8" t="inlineStr">
         <is>
           <t>Средства индивидуальной защиты головы от механических воздействий</t>
         </is>
       </c>
-      <c r="D28" s="8" t="inlineStr">
+      <c r="D30" s="8" t="inlineStr">
         <is>
           <t>Каска защитная</t>
         </is>
       </c>
-      <c r="E28" s="9" t="inlineStr">
+      <c r="E30" s="9" t="inlineStr">
         <is>
           <t>1 шт. на 2 года</t>
         </is>
       </c>
-      <c r="F28" s="8" t="inlineStr">
+      <c r="F30" s="8" t="inlineStr">
         <is>
           <t>Приложение №2 ЕТН, п.1.3.1</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" s="6" t="n">
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>Слесарь-сборщик</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
+      <c r="C31" s="8" t="inlineStr">
         <is>
           <t>Одежда специальная защитная</t>
         </is>
       </c>
-      <c r="D29" s="8" t="inlineStr">
+      <c r="D31" s="8" t="inlineStr">
         <is>
           <t>Костюм для защиты от механических воздействий (истирания) (Ми)</t>
         </is>
       </c>
-      <c r="E29" s="9" t="inlineStr">
+      <c r="E31" s="9" t="inlineStr">
         <is>
           <t>1 шт. на 1 год</t>
         </is>
       </c>
-      <c r="F29" s="8" t="inlineStr">
+      <c r="F31" s="8" t="inlineStr">
         <is>
           <t>Приложение №1 ЕТН, п.4562</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="40.5" customHeight="1">
-      <c r="A30" s="13" t="n"/>
-      <c r="B30" s="13" t="n"/>
-      <c r="C30" s="8" t="inlineStr">
-        <is>
-          <t>Средства защиты ног</t>
-        </is>
-      </c>
-      <c r="D30" s="8" t="inlineStr">
-        <is>
-          <t>Обувь специальная для защиты от механических воздействий (ударов в носочной части 200 Дж), с маслобензостойкой противоскользящей подошвой (Мун200)</t>
-        </is>
-      </c>
-      <c r="E30" s="9" t="inlineStr">
-        <is>
-          <t>1 пара на 1 год</t>
-        </is>
-      </c>
-      <c r="F30" s="13" t="n"/>
-    </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="13" t="n"/>
-      <c r="B31" s="13" t="n"/>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>Средства защиты рук</t>
-        </is>
-      </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>Перчатки для защиты от механических воздействий (истирания) (Ми)</t>
-        </is>
-      </c>
-      <c r="E31" s="9" t="inlineStr">
-        <is>
-          <t>12 пар на 1 год</t>
-        </is>
-      </c>
-      <c r="F31" s="13" t="n"/>
-    </row>
-    <row r="32" ht="15" customHeight="1">
+    <row r="32" ht="40.5" customHeight="1">
       <c r="A32" s="13" t="n"/>
       <c r="B32" s="13" t="n"/>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Средства защиты головы</t>
+          <t>Средства защиты ног</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>Головной убор для защиты от общих производственных загрязнений</t>
+          <t>Обувь специальная для защиты от механических воздействий (ударов в носочной части 200 Дж), с маслобензостойкой противоскользящей подошвой (Мун200)</t>
         </is>
       </c>
       <c r="E32" s="9" t="inlineStr">
         <is>
-          <t>1 шт. на 1 год</t>
+          <t>1 пара на 1 год</t>
         </is>
       </c>
       <c r="F32" s="13" t="n"/>
     </row>
-    <row r="33" ht="27" customHeight="1">
+    <row r="33" ht="15" customHeight="1">
       <c r="A33" s="13" t="n"/>
       <c r="B33" s="13" t="n"/>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>Средства защиты глаз</t>
+          <t>Средства защиты рук</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>Очки защитные от механических воздействий, в том числе с покрытием от запотевания</t>
+          <t>Перчатки для защиты от механических воздействий (истирания) (Ми)</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>1 шт. на 1 год</t>
-        </is>
-      </c>
-      <c r="F33" s="11" t="n"/>
-    </row>
-    <row r="34" ht="27" customHeight="1">
+          <t>12 пар на 1 год</t>
+        </is>
+      </c>
+      <c r="F33" s="13" t="n"/>
+    </row>
+    <row r="34" ht="15" customHeight="1">
       <c r="A34" s="13" t="n"/>
       <c r="B34" s="13" t="n"/>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Средства индивидуальной защиты органа слуха</t>
+          <t>Средства защиты головы</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Противошумные вкладыши (беруши) многоразовые</t>
+          <t>Головной убор для защиты от общих производственных загрязнений</t>
         </is>
       </c>
       <c r="E34" s="9" t="inlineStr">
         <is>
-          <t>12 пар на 1 год (1 пара на 1 месяц)</t>
-        </is>
-      </c>
-      <c r="F34" s="8" t="inlineStr">
-        <is>
-          <t>Приложение №2 ЕТН, п.10.1.1 (опасность идентифицирована по результатам ОПР)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1">
+          <t>1 шт. на 1 год</t>
+        </is>
+      </c>
+      <c r="F34" s="13" t="n"/>
+    </row>
+    <row r="35" ht="27" customHeight="1">
       <c r="A35" s="13" t="n"/>
       <c r="B35" s="13" t="n"/>
-      <c r="C35" s="8" t="n"/>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>Средства защиты глаз</t>
+        </is>
+      </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>или Противошумные наушники</t>
+          <t>Очки защитные от механических воздействий, в том числе с покрытием от запотевания</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
@@ -2390,113 +2422,105 @@
       </c>
       <c r="F35" s="11" t="n"/>
     </row>
-    <row r="36" ht="15" customHeight="1">
+    <row r="36" ht="27" customHeight="1">
       <c r="A36" s="13" t="n"/>
       <c r="B36" s="13" t="n"/>
-      <c r="C36" s="12" t="inlineStr">
-        <is>
-          <t>При сверлении, зачистке, опиловке деталей из композиционных материалов и пластиков:</t>
-        </is>
-      </c>
-      <c r="D36" s="17" t="n"/>
-      <c r="E36" s="17" t="n"/>
-      <c r="F36" s="18" t="n"/>
-    </row>
-    <row r="37" ht="54" customHeight="1">
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>Средства индивидуальной защиты органа слуха</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>Противошумные вкладыши (беруши) многоразовые</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>12 пар на 1 год (1 пара на 1 месяц)</t>
+        </is>
+      </c>
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t>Приложение №2 ЕТН, п.10.1.1 (опасность идентифицирована по результатам ОПР)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1">
       <c r="A37" s="13" t="n"/>
       <c r="B37" s="13" t="n"/>
-      <c r="C37" s="8" t="inlineStr">
-        <is>
-          <t>Средства индивидуальной защиты органов дыхания фильтрующего типа противоаэрозольные</t>
-        </is>
-      </c>
+      <c r="C37" s="8" t="n"/>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>Противоаэрозольные средства индивидуальной защиты органов дыхания с фильтрующей лицевой частью - фильтрующие полумаски одноразовые, класс защиты не ниже FFP2</t>
+          <t>или Противошумные наушники</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t>1 шт. на смену выполнения указанных работ, не более 247 шт. на 1 год</t>
-        </is>
-      </c>
-      <c r="F37" s="8" t="inlineStr">
-        <is>
-          <t>Приложение №2 ЕТН, п.7.1.2</t>
-        </is>
-      </c>
+          <t>1 шт. на 1 год</t>
+        </is>
+      </c>
+      <c r="F37" s="11" t="n"/>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" s="13" t="n"/>
       <c r="B38" s="13" t="n"/>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>При работе с клеями, герметиками, обезжиривающими составами:</t>
+          <t>При сверлении, зачистке, опиловке деталей из композиционных материалов и пластиков:</t>
         </is>
       </c>
       <c r="D38" s="17" t="n"/>
       <c r="E38" s="17" t="n"/>
       <c r="F38" s="18" t="n"/>
     </row>
-    <row r="39" ht="27" customHeight="1">
+    <row r="39" ht="54" customHeight="1">
       <c r="A39" s="13" t="n"/>
       <c r="B39" s="13" t="n"/>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>Средства индивидуальной защиты глаз от химических факторов</t>
+          <t>Средства индивидуальной защиты органов дыхания фильтрующего типа противоаэрозольные</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>Очки защитные закрытого типа</t>
+          <t>Противоаэрозольные средства индивидуальной защиты органов дыхания с фильтрующей лицевой частью - фильтрующие полумаски одноразовые, класс защиты не ниже FFP2</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
         <is>
-          <t>1 шт. на 1 год</t>
+          <t>1 шт. на смену выполнения указанных работ, не более 247 шт. на 1 год</t>
         </is>
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>Приложение №2 ЕТН, п.6.5.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="27" customHeight="1">
+          <t>Приложение №2 ЕТН, п.7.1.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1">
       <c r="A40" s="13" t="n"/>
       <c r="B40" s="13" t="n"/>
-      <c r="C40" s="8" t="inlineStr">
-        <is>
-          <t>Средства защиты рук</t>
-        </is>
-      </c>
-      <c r="D40" s="8" t="inlineStr">
-        <is>
-          <t>Перчатки для защиты от химических факторов (нитриловые), стойкие к применяемым веществам согласно паспортам безопасности</t>
-        </is>
-      </c>
-      <c r="E40" s="9" t="inlineStr">
-        <is>
-          <t>12 пар на 1 год</t>
-        </is>
-      </c>
-      <c r="F40" s="8" t="inlineStr">
-        <is>
-          <t>Приложение №2 ЕТН, п.6.9</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="15" customHeight="1">
+      <c r="C40" s="12" t="inlineStr">
+        <is>
+          <t>При работе с клеями, герметиками, обезжиривающими составами:</t>
+        </is>
+      </c>
+      <c r="D40" s="17" t="n"/>
+      <c r="E40" s="17" t="n"/>
+      <c r="F40" s="18" t="n"/>
+    </row>
+    <row r="41" ht="27" customHeight="1">
       <c r="A41" s="13" t="n"/>
       <c r="B41" s="13" t="n"/>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>Одежда специальная защитная</t>
+          <t>Средства индивидуальной защиты глаз от химических факторов</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>Фартук для защиты от общих производственных загрязнений</t>
+          <t>Очки защитные закрытого типа</t>
         </is>
       </c>
       <c r="E41" s="9" t="inlineStr">
@@ -2506,127 +2530,156 @@
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>Приложение №2 ЕТН, п.2.1.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="15" customHeight="1">
+          <t>Приложение №2 ЕТН, п.6.5.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="27" customHeight="1">
       <c r="A42" s="13" t="n"/>
       <c r="B42" s="13" t="n"/>
-      <c r="C42" s="12" t="inlineStr">
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>Средства защиты рук</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>Перчатки для защиты от химических факторов (нитриловые), стойкие к применяемым веществам согласно паспортам безопасности</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="inlineStr">
+        <is>
+          <t>12 пар на 1 год</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t>Приложение №2 ЕТН, п.6.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="15" customHeight="1">
+      <c r="A43" s="13" t="n"/>
+      <c r="B43" s="13" t="n"/>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>Одежда специальная защитная</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>Фартук для защиты от общих производственных загрязнений</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="inlineStr">
+        <is>
+          <t>1 шт. на 1 год</t>
+        </is>
+      </c>
+      <c r="F43" s="8" t="inlineStr">
+        <is>
+          <t>Приложение №2 ЕТН, п.2.1.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="15" customHeight="1">
+      <c r="A44" s="13" t="n"/>
+      <c r="B44" s="13" t="n"/>
+      <c r="C44" s="12" t="inlineStr">
         <is>
           <t>При допуске к управлению подъёмными сооружениями (кран-балка, таль) с пола:</t>
         </is>
       </c>
-      <c r="D42" s="17" t="n"/>
-      <c r="E42" s="17" t="n"/>
-      <c r="F42" s="18" t="n"/>
-    </row>
-    <row r="43" ht="27" customHeight="1">
-      <c r="A43" s="11" t="n"/>
-      <c r="B43" s="11" t="n"/>
-      <c r="C43" s="8" t="inlineStr">
+      <c r="D44" s="17" t="n"/>
+      <c r="E44" s="17" t="n"/>
+      <c r="F44" s="18" t="n"/>
+    </row>
+    <row r="45" ht="27" customHeight="1">
+      <c r="A45" s="11" t="n"/>
+      <c r="B45" s="11" t="n"/>
+      <c r="C45" s="8" t="inlineStr">
         <is>
           <t>Средства индивидуальной защиты головы от механических воздействий</t>
         </is>
       </c>
-      <c r="D43" s="8" t="inlineStr">
+      <c r="D45" s="8" t="inlineStr">
         <is>
           <t>Каска защитная</t>
         </is>
       </c>
-      <c r="E43" s="9" t="inlineStr">
+      <c r="E45" s="9" t="inlineStr">
         <is>
           <t>1 шт. на 2 года</t>
         </is>
       </c>
-      <c r="F43" s="8" t="inlineStr">
+      <c r="F45" s="8" t="inlineStr">
         <is>
           <t>Приложение №2 ЕТН, п.1.3.1</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="15" customHeight="1"/>
-    <row r="45" ht="15" customHeight="1">
-      <c r="B45" s="14" t="inlineStr">
+    <row r="46" ht="15" customHeight="1"/>
+    <row r="47" ht="15" customHeight="1">
+      <c r="B47" s="14" t="inlineStr">
         <is>
           <t>Примечания:</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="30" customHeight="1">
-      <c r="B46" s="15" t="inlineStr">
-        <is>
-          <t>1. Выдаются СИЗ, имеющие действующий сертификат или декларацию соответствия ТР ТС 019/2011 (п.7 Правил, приказ №766н), с защитными свойствами, указанными в графе 4.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="30" customHeight="1">
-      <c r="B47" s="15" t="inlineStr">
-        <is>
-          <t>2. СИЗ органа слуха установлены по результатам ОПР (опасность «повышенный уровень шума», п.10.1 Приложения №2 ЕТН). СОУТ по фактору «шум» не проводилась: после проведения СОУТ (измерений) эффективность СИЗ (SNR) подтверждается по фактическому уровню шума, нормы актуализируются (п.19 Правил).</t>
         </is>
       </c>
     </row>
     <row r="48" ht="30" customHeight="1">
       <c r="B48" s="15" t="inlineStr">
         <is>
-          <t>3. Работа в перчатках на станках с вращающимися частями (шпиндель, патрон, заготовка) запрещена (Правила по охране труда при обработке металлов, приказ Минтруда России №887н). Перчатки применяются при установке/снятии заготовок, уборке стружки, слесарных операциях.</t>
+          <t>1. Выдаются СИЗ, имеющие действующий сертификат или декларацию соответствия ТР ТС 019/2011 (п.7 Правил, приказ №766н), с защитными свойствами, указанными в графе 4.</t>
         </is>
       </c>
     </row>
     <row r="49" ht="30" customHeight="1">
       <c r="B49" s="15" t="inlineStr">
         <is>
-          <t>4. СИЗ по строкам «При …» выдаются работникам, фактически выполняющим указанные работы (перечень утверждается распоряжением по участку).</t>
+          <t>2. СИЗ органа слуха установлены по результатам ОПР (опасность «повышенный уровень шума», п.10.1 Приложения №2 ЕТН). СОУТ по фактору «шум» не проводилась: после проведения СОУТ (измерений) эффективность СИЗ (SNR) подтверждается по фактическому уровню шума, нормы актуализируются (п.19 Правил).</t>
         </is>
       </c>
     </row>
     <row r="50" ht="30" customHeight="1">
       <c r="B50" s="15" t="inlineStr">
         <is>
-          <t>5. Количество одноразовых СИЗ органов дыхания и сменных фильтров рассчитано на 247 рабочих смен (производственный календарь 2026 г., пятидневная рабочая неделя).</t>
+          <t>3. Работа в перчатках на сверлильных и других станках с вращающимися частями запрещена (раздел LXXVI Правил по охране труда при обработке металлов, приказ Минтруда России №887н).</t>
         </is>
       </c>
     </row>
     <row r="51" ht="30" customHeight="1">
       <c r="B51" s="15" t="inlineStr">
         <is>
+          <t>4. СИЗ по строкам «При …» выдаются работникам, фактически выполняющим указанные работы (перечень утверждается распоряжением по участку).</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="B52" s="15" t="inlineStr">
+        <is>
+          <t>5. Количество одноразовых СИЗ органов дыхания рассчитано на 247 рабочих смен (производственный календарь 2026 г., пятидневная рабочая неделя). СИЗ, выдаваемые 1 раз в месяц и чаще, выдаются с учетом времени, фактически отработанного на рабочем месте, без учета отпусков (п.58 Правил).</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="30" customHeight="1">
+      <c r="B53" s="15" t="inlineStr">
+        <is>
           <t>6. Нормы подлежат сверке с результатами СОУТ и ОПР и актуализации при их изменении (п.14, п.19 Правил, приказ №766н).</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="15" customHeight="1"/>
-    <row r="53" ht="15" customHeight="1">
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>Разработал:</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="32" customHeight="1">
-      <c r="B54" s="16" t="inlineStr">
-        <is>
-          <t>Начальник отдела охраны труда и промышленной безопасности</t>
-        </is>
-      </c>
-      <c r="D54" s="16" t="inlineStr">
-        <is>
-          <t>________________ / ____________</t>
-        </is>
-      </c>
-    </row>
+    <row r="54" ht="15" customHeight="1"/>
     <row r="55" ht="15" customHeight="1">
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Согласовано:</t>
+          <t>Разработал:</t>
         </is>
       </c>
     </row>
     <row r="56" ht="32" customHeight="1">
       <c r="B56" s="16" t="inlineStr">
         <is>
-          <t>Директор по производству</t>
+          <t>Начальник отдела охраны труда и промышленной безопасности</t>
         </is>
       </c>
       <c r="D56" s="16" t="inlineStr">
@@ -2635,22 +2688,17 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="32" customHeight="1">
-      <c r="B57" s="16" t="inlineStr">
-        <is>
-          <t>Начальник участка</t>
-        </is>
-      </c>
-      <c r="D57" s="16" t="inlineStr">
-        <is>
-          <t>________________ / ____________</t>
+    <row r="57" ht="15" customHeight="1">
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>Согласовано:</t>
         </is>
       </c>
     </row>
     <row r="58" ht="32" customHeight="1">
       <c r="B58" s="16" t="inlineStr">
         <is>
-          <t>Мастер участка</t>
+          <t>Директор по производству</t>
         </is>
       </c>
       <c r="D58" s="16" t="inlineStr">
@@ -2662,10 +2710,34 @@
     <row r="59" ht="32" customHeight="1">
       <c r="B59" s="16" t="inlineStr">
         <is>
+          <t>Начальник участка</t>
+        </is>
+      </c>
+      <c r="D59" s="16" t="inlineStr">
+        <is>
+          <t>________________ / ____________</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="32" customHeight="1">
+      <c r="B60" s="16" t="inlineStr">
+        <is>
+          <t>Мастер участка</t>
+        </is>
+      </c>
+      <c r="D60" s="16" t="inlineStr">
+        <is>
+          <t>________________ / ____________</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="32" customHeight="1">
+      <c r="B61" s="16" t="inlineStr">
+        <is>
           <t>Представитель выборного органа первичной профсоюзной организации (при наличии)</t>
         </is>
       </c>
-      <c r="D59" s="16" t="inlineStr">
+      <c r="D61" s="16" t="inlineStr">
         <is>
           <t>________________ / ____________</t>
         </is>
@@ -2675,39 +2747,39 @@
   <mergeCells count="35">
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="B7:F7"/>
-    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B31:B45"/>
     <mergeCell ref="B47:F47"/>
-    <mergeCell ref="F25:F26"/>
-    <mergeCell ref="B13:B19"/>
     <mergeCell ref="B59:C59"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="B13:B21"/>
     <mergeCell ref="C38:F38"/>
-    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="F22:F26"/>
     <mergeCell ref="B56:C56"/>
+    <mergeCell ref="F31:F35"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="B52:F52"/>
     <mergeCell ref="B58:C58"/>
-    <mergeCell ref="C18:F18"/>
     <mergeCell ref="B48:F48"/>
-    <mergeCell ref="A13:A19"/>
-    <mergeCell ref="F34:F35"/>
+    <mergeCell ref="A22:A30"/>
     <mergeCell ref="D4:F4"/>
-    <mergeCell ref="A20:A28"/>
+    <mergeCell ref="B61:C61"/>
     <mergeCell ref="D3:F3"/>
-    <mergeCell ref="B29:B43"/>
-    <mergeCell ref="C42:F42"/>
-    <mergeCell ref="F29:F33"/>
-    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="A13:A21"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="F27:F28"/>
     <mergeCell ref="D5:F5"/>
-    <mergeCell ref="B20:B28"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C29:F29"/>
     <mergeCell ref="D1:F1"/>
+    <mergeCell ref="C44:F44"/>
     <mergeCell ref="B49:F49"/>
-    <mergeCell ref="F20:F24"/>
+    <mergeCell ref="B22:B30"/>
+    <mergeCell ref="C40:F40"/>
     <mergeCell ref="C9:F9"/>
-    <mergeCell ref="A29:A43"/>
     <mergeCell ref="B51:F51"/>
-    <mergeCell ref="B45:F45"/>
-    <mergeCell ref="C27:F27"/>
     <mergeCell ref="B50:F50"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="A31:A45"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -2720,7 +2792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.3" customWidth="1" min="1" max="1"/>
@@ -2789,7 +2861,7 @@
       </c>
     </row>
     <row r="10" ht="15" customHeight="1"/>
-    <row r="11" ht="64" customHeight="1">
+    <row r="11" ht="67.5" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
           <t>№ п/п</t>
@@ -2797,7 +2869,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Должность работника</t>
+          <t>Наименование профессии (должности)</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -2812,12 +2884,12 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Нормы выдачи на год (период), единицы измерения (штуки, пары, комплекты)</t>
+          <t>Нормы выдачи с указанием периодичности выдачи, количества на период, единицы измерения (штуки, пары, комплекты, г, мл.)</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Основание выдачи СИЗ (пункты Единых типовых норм (ЕТН), правил по охране труда и иных документов)</t>
+          <t>Основание выдачи СИЗ (пункты Единых типовых норм, правил по охране труда и иных документов)</t>
         </is>
       </c>
     </row>
@@ -2895,131 +2967,131 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="27" customHeight="1">
-      <c r="A15" s="11" t="n"/>
-      <c r="B15" s="11" t="n"/>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" s="13" t="n"/>
+      <c r="B15" s="13" t="n"/>
       <c r="C15" s="8" t="inlineStr">
         <is>
+          <t>Средства защиты рук</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>Перчатки для защиты от механических воздействий (истирания) (Ми)</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>12 пар на 1 год</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="n"/>
+    </row>
+    <row r="16" ht="27" customHeight="1">
+      <c r="A16" s="11" t="n"/>
+      <c r="B16" s="11" t="n"/>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
           <t>Средства защиты головы</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>Головной убор для защиты от общих производственных загрязнений (косынка, шапочка)</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr">
+      <c r="E16" s="9" t="inlineStr">
         <is>
           <t>1 шт. на 1 год</t>
         </is>
       </c>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="F16" s="8" t="inlineStr">
         <is>
           <t>Приложение №2 ЕТН, п.2.1.1</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="54" customHeight="1">
-      <c r="A16" s="6" t="n">
+    <row r="17" ht="54" customHeight="1">
+      <c r="A17" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>Специалист по пошиву</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>Одежда специальная защитная</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t>Костюм для защиты от механических воздействий (истирания) (Ми)</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E17" s="9" t="inlineStr">
         <is>
           <t>1 шт. на 1 год</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="F17" s="8" t="inlineStr">
         <is>
           <t>Приложение №1 ЕТН, п.5145 «Швея» (по аналогии выполняемых работ); п.18 Правил обеспечения работников СИЗ (приказ Минтруда №766н)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="27" customHeight="1">
-      <c r="A17" s="13" t="n"/>
-      <c r="B17" s="13" t="n"/>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>Средства защиты ног</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>Обувь специальная для защиты от механических воздействий (истирания) (Ми)</t>
-        </is>
-      </c>
-      <c r="E17" s="9" t="inlineStr">
-        <is>
-          <t>1 пара на 1 год</t>
-        </is>
-      </c>
-      <c r="F17" s="13" t="n"/>
-    </row>
-    <row r="18" ht="15" customHeight="1">
+    <row r="18" ht="27" customHeight="1">
       <c r="A18" s="13" t="n"/>
       <c r="B18" s="13" t="n"/>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Средства защиты рук</t>
+          <t>Средства защиты ног</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Перчатки для защиты от механических воздействий (истирания) (Ми)</t>
+          <t>Обувь специальная для защиты от механических воздействий (истирания) (Ми)</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>12 пар на 1 год</t>
+          <t>1 пара на 1 год</t>
         </is>
       </c>
       <c r="F18" s="13" t="n"/>
     </row>
-    <row r="19" ht="27" customHeight="1">
+    <row r="19" ht="15" customHeight="1">
       <c r="A19" s="13" t="n"/>
       <c r="B19" s="13" t="n"/>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>Средства защиты головы</t>
+          <t>Средства защиты рук</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>Головной убор для защиты от общих производственных загрязнений (косынка, шапочка)</t>
+          <t>Перчатки для защиты от механических воздействий (истирания) (Ми)</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>1 шт. на 1 год</t>
-        </is>
-      </c>
-      <c r="F19" s="11" t="n"/>
-    </row>
-    <row r="20" ht="15" customHeight="1">
+          <t>12 пар на 1 год</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="n"/>
+    </row>
+    <row r="20" ht="27" customHeight="1">
       <c r="A20" s="13" t="n"/>
       <c r="B20" s="13" t="n"/>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Одежда специальная защитная</t>
+          <t>Средства защиты головы</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Фартук для защиты от общих производственных загрязнений</t>
+          <t>Головной убор для защиты от общих производственных загрязнений (косынка, шапочка)</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
@@ -3027,69 +3099,65 @@
           <t>1 шт. на 1 год</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>Приложение №2 ЕТН, п.2.1.2</t>
-        </is>
-      </c>
+      <c r="F20" s="11" t="n"/>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" s="13" t="n"/>
       <c r="B21" s="13" t="n"/>
-      <c r="C21" s="12" t="inlineStr">
-        <is>
-          <t>При раскрое и пошиве материалов, выделяющих волокна и пыль (стеклоткань, арамидные, огнестойкие ткани, препреги):</t>
-        </is>
-      </c>
-      <c r="D21" s="17" t="n"/>
-      <c r="E21" s="17" t="n"/>
-      <c r="F21" s="18" t="n"/>
-    </row>
-    <row r="22" ht="54" customHeight="1">
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Одежда специальная защитная</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>Фартук для защиты от общих производственных загрязнений</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>1 шт. на 1 год</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>Приложение №2 ЕТН, п.2.1.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
       <c r="A22" s="13" t="n"/>
       <c r="B22" s="13" t="n"/>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>Средства индивидуальной защиты органов дыхания фильтрующего типа противоаэрозольные</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>Противоаэрозольные средства индивидуальной защиты органов дыхания с фильтрующей лицевой частью - фильтрующие полумаски одноразовые, класс защиты не ниже FFP2</t>
-        </is>
-      </c>
-      <c r="E22" s="9" t="inlineStr">
-        <is>
-          <t>1 шт. на смену выполнения указанных работ, не более 247 шт. на 1 год</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t>Приложение №2 ЕТН, п.7.1.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="40.5" customHeight="1">
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>При раскрое и пошиве материалов, выделяющих волокна и пыль (стеклоткань, арамидные, огнестойкие ткани, препреги):</t>
+        </is>
+      </c>
+      <c r="D22" s="17" t="n"/>
+      <c r="E22" s="17" t="n"/>
+      <c r="F22" s="18" t="n"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
       <c r="A23" s="13" t="n"/>
       <c r="B23" s="13" t="n"/>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Средства индивидуальной защиты глаз от механических воздействий, от грубодисперсных аэрозолей (пыли)</t>
+          <t>Средства индивидуальной защиты органов дыхания фильтрующего типа противоаэрозольные</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>Очки защитные закрытые с непрямой вентиляцией, с покрытием от запотевания</t>
+          <t>Противоаэрозольные средства индивидуальной защиты органов дыхания с фильтрующей лицевой частью - фильтрующие полумаски одноразовые, класс защиты не ниже FFP2</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>2 шт. на 1 год (включая 1 резервную)</t>
+          <t>1 шт. на смену выполнения указанных работ, не более 247 шт. на 1 год</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t>Приложение №2 ЕТН, п.7.1.1; п.16 Правил (приказ №766н)</t>
+          <t>Приложение №2 ЕТН, п.7.1.2</t>
         </is>
       </c>
     </row>
@@ -3098,22 +3166,22 @@
       <c r="B24" s="13" t="n"/>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Средства защиты рук</t>
+          <t>Средства индивидуальной защиты глаз от механических воздействий, от грубодисперсных аэрозолей (пыли)</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Перчатки для защиты от механических воздействий (истирания), трикотажные плотной вязки с полимерным покрытием (Ми)</t>
+          <t>Очки защитные закрытые с непрямой вентиляцией, с покрытием от запотевания</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>60 пар на 1 год (включая 12 пар по основной норме)</t>
+          <t>2 шт. на 1 год (включая 1 резервную)</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
         <is>
-          <t>Приложение №2 ЕТН, п.1.28; п.16 Правил (приказ №766н)</t>
+          <t>Приложение №2 ЕТН, п.7.1.1; п.16 Правил (приказ №766н)</t>
         </is>
       </c>
     </row>
@@ -3122,130 +3190,152 @@
       <c r="B25" s="13" t="n"/>
       <c r="C25" s="8" t="inlineStr">
         <is>
+          <t>Средства защиты рук</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>Перчатки для защиты от механических воздействий (истирания), трикотажные плотной вязки с полимерным покрытием (Ми)</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>60 пар на 1 год (включая 12 пар по основной норме)</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>Приложение №2 ЕТН, п.1.28; п.16 Правил (приказ №766н)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="40.5" customHeight="1">
+      <c r="A26" s="13" t="n"/>
+      <c r="B26" s="13" t="n"/>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
           <t>Одежда специальная защитная</t>
         </is>
       </c>
-      <c r="D25" s="8" t="inlineStr">
+      <c r="D26" s="8" t="inlineStr">
         <is>
           <t>Фартук из плотной гладкой ткани с ПВХ-покрытием (или полиэфирной ткани с водоотталкивающей пропиткой)</t>
         </is>
       </c>
-      <c r="E25" s="9" t="inlineStr">
+      <c r="E26" s="9" t="inlineStr">
         <is>
           <t>2 шт. на 1 год (включая 1 шт. по основной норме)</t>
         </is>
       </c>
-      <c r="F25" s="8" t="inlineStr">
+      <c r="F26" s="8" t="inlineStr">
         <is>
           <t>Приложение №2 ЕТН, п.2.1.2</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="40.5" customHeight="1">
-      <c r="A26" s="11" t="n"/>
-      <c r="B26" s="11" t="n"/>
-      <c r="C26" s="8" t="inlineStr">
+    <row r="27" ht="40.5" customHeight="1">
+      <c r="A27" s="11" t="n"/>
+      <c r="B27" s="11" t="n"/>
+      <c r="C27" s="8" t="inlineStr">
         <is>
           <t>Средства защиты головы</t>
         </is>
       </c>
-      <c r="D26" s="8" t="inlineStr">
+      <c r="D27" s="8" t="inlineStr">
         <is>
           <t>Головной убор для защиты от общих производственных загрязнений (косынка, шапочка)</t>
         </is>
       </c>
-      <c r="E26" s="9" t="inlineStr">
+      <c r="E27" s="9" t="inlineStr">
         <is>
           <t>4 шт. на 1 год (включая 1 шт. по основной норме)</t>
         </is>
       </c>
-      <c r="F26" s="8" t="inlineStr">
+      <c r="F27" s="8" t="inlineStr">
         <is>
           <t>Приложение №2 ЕТН, п.2.1.2; п.16 Правил (приказ №766н)</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1"/>
-    <row r="28" ht="15" customHeight="1">
-      <c r="B28" s="14" t="inlineStr">
+    <row r="28" ht="15" customHeight="1"/>
+    <row r="29" ht="15" customHeight="1">
+      <c r="B29" s="14" t="inlineStr">
         <is>
           <t>Примечания:</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="B29" s="15" t="inlineStr">
-        <is>
-          <t>1. Выдаются СИЗ, имеющие действующий сертификат или декларацию соответствия ТР ТС 019/2011 (п.7 Правил, приказ №766н), с защитными свойствами, указанными в графе 4.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>2. СИЗ органа слуха установлены по результатам ОПР (опасность «повышенный уровень шума», п.10.1 Приложения №2 ЕТН). СОУТ по фактору «шум» не проводилась: после проведения СОУТ (измерений) эффективность СИЗ (SNR) подтверждается по фактическому уровню шума, нормы актуализируются (п.19 Правил).</t>
+          <t>1. Выдаются СИЗ, имеющие действующий сертификат или декларацию соответствия ТР ТС 019/2011 (п.7 Правил, приказ №766н), с защитными свойствами, указанными в графе 4.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>3. Работа в перчатках на станках с вращающимися частями (шпиндель, патрон, заготовка) запрещена (Правила по охране труда при обработке металлов, приказ Минтруда России №887н). Перчатки применяются при установке/снятии заготовок, уборке стружки, слесарных операциях.</t>
+          <t>2. СИЗ по строкам «При …» выдаются работникам, фактически выполняющим указанные работы (перечень утверждается распоряжением по участку).</t>
         </is>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>4. СИЗ по строкам «При …» выдаются работникам, фактически выполняющим указанные работы (перечень утверждается распоряжением по участку).</t>
+          <t>3. Количество одноразовых СИЗ органов дыхания рассчитано на 247 рабочих смен (производственный календарь 2026 г., пятидневная рабочая неделя). СИЗ, выдаваемые 1 раз в месяц и чаще, выдаются с учетом времени, фактически отработанного на рабочем месте, без учета отпусков (п.58 Правил).</t>
         </is>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>5. Количество одноразовых СИЗ органов дыхания и сменных фильтров рассчитано на 247 рабочих смен (производственный календарь 2026 г., пятидневная рабочая неделя).</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="B34" s="15" t="inlineStr">
-        <is>
-          <t>6. Нормы подлежат сверке с результатами СОУТ и ОПР и актуализации при их изменении (п.14, п.19 Правил, приказ №766н).</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1"/>
-    <row r="36" ht="15" customHeight="1">
-      <c r="B36" s="4" t="inlineStr">
+          <t>4. Нормы подлежат сверке с результатами СОУТ и ОПР и актуализации при их изменении (п.14, п.19 Правил, приказ №766н).</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1"/>
+    <row r="35" ht="15" customHeight="1">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>Разработал:</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="32" customHeight="1">
-      <c r="B37" s="16" t="inlineStr">
+    <row r="36" ht="32" customHeight="1">
+      <c r="B36" s="16" t="inlineStr">
         <is>
           <t>Начальник отдела охраны труда и промышленной безопасности</t>
         </is>
       </c>
-      <c r="D37" s="16" t="inlineStr">
+      <c r="D36" s="16" t="inlineStr">
         <is>
           <t>________________ / ____________</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="15" customHeight="1">
-      <c r="B38" s="4" t="inlineStr">
+    <row r="37" ht="15" customHeight="1">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>Согласовано:</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="32" customHeight="1">
+      <c r="B38" s="16" t="inlineStr">
+        <is>
+          <t>Директор по производству</t>
+        </is>
+      </c>
+      <c r="D38" s="16" t="inlineStr">
+        <is>
+          <t>________________ / ____________</t>
         </is>
       </c>
     </row>
     <row r="39" ht="32" customHeight="1">
       <c r="B39" s="16" t="inlineStr">
         <is>
-          <t>Директор по производству</t>
+          <t>Начальник участка</t>
         </is>
       </c>
       <c r="D39" s="16" t="inlineStr">
@@ -3257,7 +3347,7 @@
     <row r="40" ht="32" customHeight="1">
       <c r="B40" s="16" t="inlineStr">
         <is>
-          <t>Начальник участка</t>
+          <t>Мастер участка</t>
         </is>
       </c>
       <c r="D40" s="16" t="inlineStr">
@@ -3269,7 +3359,7 @@
     <row r="41" ht="32" customHeight="1">
       <c r="B41" s="16" t="inlineStr">
         <is>
-          <t>Мастер участка</t>
+          <t>Представитель выборного органа первичной профсоюзной организации (при наличии)</t>
         </is>
       </c>
       <c r="D41" s="16" t="inlineStr">
@@ -3278,44 +3368,31 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="32" customHeight="1">
-      <c r="B42" s="16" t="inlineStr">
-        <is>
-          <t>Представитель выборного органа первичной профсоюзной организации (при наличии)</t>
-        </is>
-      </c>
-      <c r="D42" s="16" t="inlineStr">
-        <is>
-          <t>________________ / ____________</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="24">
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="B7:F7"/>
-    <mergeCell ref="A16:A26"/>
-    <mergeCell ref="F16:F19"/>
+    <mergeCell ref="B17:B27"/>
     <mergeCell ref="B31:F31"/>
-    <mergeCell ref="A13:A15"/>
     <mergeCell ref="B39:C39"/>
+    <mergeCell ref="A17:A27"/>
+    <mergeCell ref="F17:F20"/>
     <mergeCell ref="D4:F4"/>
-    <mergeCell ref="B42:C42"/>
     <mergeCell ref="D3:F3"/>
+    <mergeCell ref="B13:B16"/>
     <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B38:C38"/>
     <mergeCell ref="D5:F5"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B37:C37"/>
     <mergeCell ref="B41:C41"/>
     <mergeCell ref="B40:C40"/>
     <mergeCell ref="D1:F1"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="A13:A16"/>
+    <mergeCell ref="C9:F9"/>
     <mergeCell ref="B30:F30"/>
-    <mergeCell ref="C9:F9"/>
     <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B13:B15"/>
-    <mergeCell ref="B16:B26"/>
-    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="B32:F32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3852,7 +3929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3918,7 +3995,7 @@
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>Костюм З+Ми, обувь Мун200, очки, СИЗ органа слуха, каска (кран-балка)</t>
+          <t>Костюм З+Ми, обувь Мун200, перчатки Ми, головной убор, очки, СИЗ органа слуха, каска (кран-балка)</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
@@ -3962,7 +4039,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="67.5" customHeight="1">
+    <row r="6" ht="81" customHeight="1">
       <c r="A6" s="9" t="n">
         <v>3</v>
       </c>
@@ -3978,7 +4055,7 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>СИЗ органа слуха, щиток (сливная стружка), каска (кран-балка). Фильтрующие полумаски по ЕТН заменены на многоразовую полумаску (1 шт. на 1 год) со сменными фильтрами P1 (50 комплектов на 1 год) - равноценная защита, п.16 Правил 766н, Прил. №2 п.7.3.1</t>
+          <t>СИЗ органа слуха, щиток (сливная стружка), каска (кран-балка). Фильтрующие полумаски по ЕТН заменены на многоразовую полумаску (1 шт. на 1 год) со сменными фильтрами P1 (50 комплектов на 1 год) - равноценная защита, п.54 Правил 766н (с учетом мнения профсоюза), Прил. №2 п.7.3.1</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
@@ -4038,12 +4115,12 @@
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Костюм ОПЗ, обувь Мун200, очки, СИЗ органа слуха, каска (кран-балка)</t>
+          <t>Костюм З+Ми, обувь Мун200, перчатки Ми, головной убор, очки, СИЗ органа слуха, каска (кран-балка)</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>Воронеж: костюм и обувь от ОПЗ. Обувь усилена до защиты от ударов (перемещение крупногабаритных узлов)</t>
+          <t>Воронеж: костюм и обувь от ОПЗ. Усилено по п.18 Правил 766н (контролирует работу слесарей-сборщиков)</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
@@ -4128,7 +4205,7 @@
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>Костюм/халат З+Ми, обувь Ми, головной убор</t>
+          <t>Костюм/халат З+Ми, обувь Ми, перчатки Ми, головной убор</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
@@ -4190,23 +4267,31 @@
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>- Приказ Минтруда России от 29.10.2021 №766н (Правила): пп.7, 14, 16, 17, 18, 19, 37, 46, 47.</t>
+          <t>- Приказ Минтруда России от 29.10.2021 №766н (Правила): пп.7, 14, 16, 17, 18, 19, 37, 46, 47, 48, 50, 54, 58; Приложения №1, №4.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
         <is>
+          <t>- Приказ Минтруда России от 11.12.2020 №887н (Правила по охране труда при обработке металлов), раздел LXXVI.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
           <t>- Утвержденные нормы АО «Авиационные интерьеры – Воронеж» 2026 г. (механический, слесарный, сборки, мебельный, композиционных материалов и др. участки) - как образец формы и практики группы компаний.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A18:F18"/>
     <mergeCell ref="A15:F15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
